--- a/bm-w26.xlsx
+++ b/bm-w26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenlo\Desktop\2526_Winter_SFQ_Data\File Upload to AQA website\Regen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{139F8E74-0F73-4C21-B08E-EB1095D47A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{139F8E74-0F73-4C21-B08E-EB1095D47A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43F00831-AD35-49D2-8329-31B9C5D5CD94}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{80BE6F33-D422-4D14-BE1C-AADC7C177704}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{80BE6F33-D422-4D14-BE1C-AADC7C177704}"/>
   </bookViews>
   <sheets>
     <sheet name="School_Term_Summary_Report-SBM-" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="133">
   <si>
     <t>Academic Year</t>
   </si>
@@ -73,34 +73,19 @@
     <t>Low Response Rate Indicator</t>
   </si>
   <si>
-    <t>Response Rate (Adjusted)</t>
-  </si>
-  <si>
     <t>No. of Sections Evaluated</t>
   </si>
   <si>
     <t>Course Overall - Mean</t>
   </si>
   <si>
-    <t>Course Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Course Overall - SD</t>
   </si>
   <si>
-    <t>Course Overall - SD (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - Mean</t>
   </si>
   <si>
-    <t>Instructor Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - SD</t>
-  </si>
-  <si>
-    <t>Instructor Overall - SD (Adjusted)</t>
   </si>
   <si>
     <t>25-26</t>
@@ -1296,10 +1281,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3365DD5F-5537-4265-958E-1E14DD797E1B}">
-  <dimension ref="A1:AA72"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1366,528 +1351,513 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.40699999999999997</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>18</v>
       </c>
       <c r="S2">
-        <v>18</v>
+        <v>4.42</v>
       </c>
       <c r="T2">
-        <v>4.42</v>
+        <v>0.79</v>
+      </c>
+      <c r="U2">
+        <v>4.59</v>
       </c>
       <c r="V2">
-        <v>0.79</v>
-      </c>
-      <c r="X2">
-        <v>4.59</v>
-      </c>
-      <c r="Z2">
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="T3">
-        <v>4.5599999999999996</v>
+        <v>0.73</v>
+      </c>
+      <c r="U3">
+        <v>4.4400000000000004</v>
       </c>
       <c r="V3">
-        <v>0.73</v>
-      </c>
-      <c r="X3">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="Z3">
         <v>1.01</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.43</v>
       </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
       <c r="S4">
-        <v>2</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="T4">
-        <v>4.6900000000000004</v>
+        <v>0.5</v>
+      </c>
+      <c r="U4">
+        <v>4.74</v>
       </c>
       <c r="V4">
-        <v>0.5</v>
-      </c>
-      <c r="X4">
-        <v>4.74</v>
-      </c>
-      <c r="Z4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>0.38400000000000001</v>
       </c>
+      <c r="R5">
+        <v>12</v>
+      </c>
       <c r="S5">
-        <v>12</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="T5">
-        <v>4.4400000000000004</v>
+        <v>0.76</v>
+      </c>
+      <c r="U5">
+        <v>4.55</v>
       </c>
       <c r="V5">
-        <v>0.76</v>
-      </c>
-      <c r="X5">
-        <v>4.55</v>
-      </c>
-      <c r="Z5">
         <v>0.68</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.56100000000000005</v>
       </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
       <c r="S6">
-        <v>2</v>
+        <v>4.03</v>
       </c>
       <c r="T6">
-        <v>4.03</v>
+        <v>0.98</v>
+      </c>
+      <c r="U6">
+        <v>4.3600000000000003</v>
       </c>
       <c r="V6">
-        <v>0.98</v>
-      </c>
-      <c r="X6">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="Z6">
         <v>0.82</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1">
         <v>0.61499999999999999</v>
       </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
       <c r="S7">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T7">
-        <v>4.63</v>
+        <v>0.62</v>
+      </c>
+      <c r="U7">
+        <v>4.88</v>
       </c>
       <c r="V7">
-        <v>0.62</v>
-      </c>
-      <c r="X7">
-        <v>4.88</v>
-      </c>
-      <c r="Z7">
         <v>0.34</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>5100</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P8" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="T8">
-        <v>4.5599999999999996</v>
+        <v>0.73</v>
+      </c>
+      <c r="U8">
+        <v>4.4400000000000004</v>
       </c>
       <c r="V8">
-        <v>0.73</v>
-      </c>
-      <c r="X8">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="Z8">
         <v>1.01</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>5100</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O9">
         <v>51</v>
@@ -1896,66 +1866,66 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9">
+        <v>4.5599999999999996</v>
       </c>
       <c r="T9">
-        <v>4.5599999999999996</v>
+        <v>0.73</v>
+      </c>
+      <c r="U9">
+        <v>4.4400000000000004</v>
       </c>
       <c r="V9">
-        <v>0.73</v>
-      </c>
-      <c r="X9">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="Z9">
         <v>1.01</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>5100</v>
       </c>
       <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
         <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" t="s">
-        <v>45</v>
       </c>
       <c r="O10">
         <v>51</v>
@@ -1964,131 +1934,131 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="T10">
+        <v>0.73</v>
+      </c>
+      <c r="U10">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="S10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T10">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="V10">
-        <v>0.73</v>
-      </c>
-      <c r="X10">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="Z10">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
       <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G11">
         <v>5341</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1">
         <v>0.35899999999999999</v>
       </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
       <c r="S11">
-        <v>1</v>
+        <v>4.79</v>
       </c>
       <c r="T11">
-        <v>4.79</v>
+        <v>0.42</v>
+      </c>
+      <c r="U11">
+        <v>4.8600000000000003</v>
       </c>
       <c r="V11">
-        <v>0.42</v>
-      </c>
-      <c r="X11">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="Z11">
         <v>0.36</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>5341</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O12">
         <v>78</v>
@@ -2096,64 +2066,64 @@
       <c r="P12" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="S12" t="s">
-        <v>30</v>
+      <c r="R12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12">
+        <v>4.79</v>
       </c>
       <c r="T12">
-        <v>4.79</v>
+        <v>0.42</v>
+      </c>
+      <c r="U12">
+        <v>4.8600000000000003</v>
       </c>
       <c r="V12">
-        <v>0.42</v>
-      </c>
-      <c r="X12">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="Z12">
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>5341</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O13">
         <v>78</v>
@@ -2161,129 +2131,129 @@
       <c r="P13" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="S13" t="s">
-        <v>30</v>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>4.79</v>
       </c>
       <c r="T13">
-        <v>4.79</v>
+        <v>0.42</v>
+      </c>
+      <c r="U13">
+        <v>4.8600000000000003</v>
       </c>
       <c r="V13">
-        <v>0.42</v>
-      </c>
-      <c r="X13">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="Z13">
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>5347</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1">
         <v>0.5</v>
       </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
       <c r="S14">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T14">
-        <v>4.63</v>
+        <v>0.54</v>
+      </c>
+      <c r="U14">
+        <v>4.6500000000000004</v>
       </c>
       <c r="V14">
-        <v>0.54</v>
-      </c>
-      <c r="X14">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="Z14">
         <v>0.53</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>29</v>
       </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G15">
         <v>5347</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O15">
         <v>80</v>
@@ -2291,64 +2261,64 @@
       <c r="P15" s="1">
         <v>0.5</v>
       </c>
-      <c r="S15" t="s">
-        <v>30</v>
+      <c r="R15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15">
+        <v>4.63</v>
       </c>
       <c r="T15">
-        <v>4.63</v>
+        <v>0.54</v>
+      </c>
+      <c r="U15">
+        <v>4.6500000000000004</v>
       </c>
       <c r="V15">
-        <v>0.54</v>
-      </c>
-      <c r="X15">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="Z15">
         <v>0.53</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>29</v>
       </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G16">
         <v>5347</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O16">
         <v>80</v>
@@ -2356,132 +2326,132 @@
       <c r="P16" s="1">
         <v>0.5</v>
       </c>
-      <c r="S16" t="s">
-        <v>30</v>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.63</v>
       </c>
       <c r="T16">
-        <v>4.63</v>
+        <v>0.54</v>
+      </c>
+      <c r="U16">
+        <v>4.6500000000000004</v>
       </c>
       <c r="V16">
-        <v>0.54</v>
-      </c>
-      <c r="X16">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="Z16">
         <v>0.53</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G17">
         <v>1090</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1">
         <v>0.24399999999999999</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>3.95</v>
       </c>
       <c r="T17">
-        <v>3.95</v>
+        <v>0.97</v>
+      </c>
+      <c r="U17">
+        <v>4.32</v>
       </c>
       <c r="V17">
-        <v>0.97</v>
-      </c>
-      <c r="X17">
-        <v>4.32</v>
-      </c>
-      <c r="Z17">
         <v>0.75</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G18">
         <v>1090</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O18">
         <v>78</v>
@@ -2490,66 +2460,66 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18">
+        <v>3.95</v>
       </c>
       <c r="T18">
-        <v>3.95</v>
+        <v>0.97</v>
+      </c>
+      <c r="U18">
+        <v>4.32</v>
       </c>
       <c r="V18">
-        <v>0.97</v>
-      </c>
-      <c r="X18">
-        <v>4.32</v>
-      </c>
-      <c r="Z18">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G19">
         <v>1090</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O19">
         <v>78</v>
@@ -2558,134 +2528,134 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="Q19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19">
+        <v>3.95</v>
+      </c>
+      <c r="T19">
+        <v>0.97</v>
+      </c>
+      <c r="U19">
+        <v>4.32</v>
+      </c>
+      <c r="V19">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
         <v>33</v>
       </c>
-      <c r="S19" t="s">
-        <v>30</v>
-      </c>
-      <c r="T19">
-        <v>3.95</v>
-      </c>
-      <c r="V19">
-        <v>0.97</v>
-      </c>
-      <c r="X19">
-        <v>4.32</v>
-      </c>
-      <c r="Z19">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
-      </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G20">
         <v>1380</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1">
         <v>0.27800000000000002</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>4.41</v>
       </c>
       <c r="T20">
-        <v>4.41</v>
+        <v>0.59</v>
+      </c>
+      <c r="U20">
+        <v>4.55</v>
       </c>
       <c r="V20">
-        <v>0.59</v>
-      </c>
-      <c r="X20">
-        <v>4.55</v>
-      </c>
-      <c r="Z20">
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <v>1380</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O21">
         <v>79</v>
@@ -2694,66 +2664,66 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
-      </c>
-      <c r="S21" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R21" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21">
+        <v>4.41</v>
       </c>
       <c r="T21">
-        <v>4.41</v>
+        <v>0.59</v>
+      </c>
+      <c r="U21">
+        <v>4.55</v>
       </c>
       <c r="V21">
-        <v>0.59</v>
-      </c>
-      <c r="X21">
-        <v>4.55</v>
-      </c>
-      <c r="Z21">
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <v>1380</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K22" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M22" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O22">
         <v>79</v>
@@ -2762,131 +2732,131 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="Q22" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22">
+        <v>4.41</v>
+      </c>
+      <c r="T22">
+        <v>0.59</v>
+      </c>
+      <c r="U22">
+        <v>4.55</v>
+      </c>
+      <c r="V22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
         <v>33</v>
       </c>
-      <c r="S22" t="s">
-        <v>30</v>
-      </c>
-      <c r="T22">
-        <v>4.41</v>
-      </c>
-      <c r="V22">
-        <v>0.59</v>
-      </c>
-      <c r="X22">
-        <v>4.55</v>
-      </c>
-      <c r="Z22">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>1700</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P23" s="1">
         <v>0.34799999999999998</v>
       </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
       <c r="S23">
-        <v>1</v>
+        <v>4.43</v>
       </c>
       <c r="T23">
-        <v>4.43</v>
+        <v>0.7</v>
+      </c>
+      <c r="U23">
+        <v>4.57</v>
       </c>
       <c r="V23">
-        <v>0.7</v>
-      </c>
-      <c r="X23">
-        <v>4.57</v>
-      </c>
-      <c r="Z23">
         <v>0.63</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>1700</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O24">
         <v>198</v>
@@ -2894,64 +2864,64 @@
       <c r="P24" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="S24" t="s">
-        <v>30</v>
+      <c r="R24" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24">
+        <v>4.43</v>
       </c>
       <c r="T24">
-        <v>4.43</v>
+        <v>0.7</v>
+      </c>
+      <c r="U24">
+        <v>4.57</v>
       </c>
       <c r="V24">
-        <v>0.7</v>
-      </c>
-      <c r="X24">
-        <v>4.57</v>
-      </c>
-      <c r="Z24">
         <v>0.63</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>1700</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K25" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M25" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O25">
         <v>198</v>
@@ -2959,132 +2929,132 @@
       <c r="P25" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="S25" t="s">
-        <v>30</v>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25">
+        <v>4.43</v>
       </c>
       <c r="T25">
-        <v>4.43</v>
+        <v>0.7</v>
+      </c>
+      <c r="U25">
+        <v>4.57</v>
       </c>
       <c r="V25">
-        <v>0.7</v>
-      </c>
-      <c r="X25">
-        <v>4.57</v>
-      </c>
-      <c r="Z25">
         <v>0.63</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>2400</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P26" s="1">
         <v>0.28000000000000003</v>
       </c>
       <c r="Q26" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
       </c>
       <c r="S26">
-        <v>1</v>
+        <v>4.07</v>
       </c>
       <c r="T26">
-        <v>4.07</v>
+        <v>0.9</v>
+      </c>
+      <c r="U26">
+        <v>4.3600000000000003</v>
       </c>
       <c r="V26">
-        <v>0.9</v>
-      </c>
-      <c r="X26">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="Z26">
         <v>0.83</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G27">
         <v>2400</v>
       </c>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -3093,66 +3063,66 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q27" t="s">
-        <v>33</v>
-      </c>
-      <c r="S27" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R27" t="s">
+        <v>25</v>
+      </c>
+      <c r="S27">
+        <v>4.07</v>
       </c>
       <c r="T27">
-        <v>4.07</v>
+        <v>0.9</v>
+      </c>
+      <c r="U27">
+        <v>4.3600000000000003</v>
       </c>
       <c r="V27">
-        <v>0.9</v>
-      </c>
-      <c r="X27">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="Z27">
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G28">
         <v>2400</v>
       </c>
       <c r="H28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="J28" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K28" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M28" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N28" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -3161,134 +3131,134 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q28" t="s">
+        <v>28</v>
+      </c>
+      <c r="R28" t="s">
+        <v>25</v>
+      </c>
+      <c r="S28">
+        <v>4.07</v>
+      </c>
+      <c r="T28">
+        <v>0.9</v>
+      </c>
+      <c r="U28">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="V28">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
         <v>33</v>
       </c>
-      <c r="S28" t="s">
-        <v>30</v>
-      </c>
-      <c r="T28">
-        <v>4.07</v>
-      </c>
-      <c r="V28">
-        <v>0.9</v>
-      </c>
-      <c r="X28">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="Z28">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
-      </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G29">
         <v>4010</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" s="1">
         <v>0.435</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="T29">
+        <v>0.32</v>
+      </c>
+      <c r="U29">
         <v>4.9000000000000004</v>
       </c>
       <c r="V29">
         <v>0.32</v>
       </c>
-      <c r="X29">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="Z29">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G30">
         <v>4010</v>
       </c>
       <c r="H30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O30">
         <v>23</v>
@@ -3297,66 +3267,66 @@
         <v>0.435</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
-      </c>
-      <c r="S30" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R30" t="s">
+        <v>25</v>
+      </c>
+      <c r="S30">
+        <v>4.9000000000000004</v>
       </c>
       <c r="T30">
+        <v>0.32</v>
+      </c>
+      <c r="U30">
         <v>4.9000000000000004</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
-      <c r="X30">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="Z30">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G31">
         <v>4010</v>
       </c>
       <c r="H31" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J31" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K31" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N31" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O31">
         <v>23</v>
@@ -3365,134 +3335,134 @@
         <v>0.435</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
-      </c>
-      <c r="S31" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R31" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31">
+        <v>4.9000000000000004</v>
       </c>
       <c r="T31">
+        <v>0.32</v>
+      </c>
+      <c r="U31">
         <v>4.9000000000000004</v>
       </c>
       <c r="V31">
         <v>0.32</v>
       </c>
-      <c r="X31">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="Z31">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G32">
         <v>4740</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I32" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P32" s="1">
         <v>0.36399999999999999</v>
       </c>
       <c r="Q32" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
       </c>
       <c r="S32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>4.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>4.5</v>
-      </c>
-      <c r="Z32">
         <v>0.76</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G33">
         <v>4740</v>
       </c>
       <c r="H33" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J33" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O33">
         <v>22</v>
@@ -3501,66 +3471,66 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="Q33" t="s">
-        <v>33</v>
-      </c>
-      <c r="S33" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R33" t="s">
+        <v>25</v>
+      </c>
+      <c r="S33">
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>4.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>4.5</v>
-      </c>
-      <c r="Z33">
         <v>0.76</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G34">
         <v>4740</v>
       </c>
       <c r="H34" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J34" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N34" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O34">
         <v>22</v>
@@ -3569,131 +3539,131 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="Q34" t="s">
+        <v>28</v>
+      </c>
+      <c r="R34" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34">
+        <v>5</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>4.5</v>
+      </c>
+      <c r="V34">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
         <v>33</v>
       </c>
-      <c r="S34" t="s">
-        <v>30</v>
-      </c>
-      <c r="T34">
-        <v>5</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>4.5</v>
-      </c>
-      <c r="Z34">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" t="s">
-        <v>38</v>
-      </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G35">
         <v>5220</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I35" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O35" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P35" s="1">
         <v>0.64600000000000002</v>
       </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
       <c r="S35">
-        <v>1</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="T35">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U35">
+        <v>4.58</v>
       </c>
       <c r="V35">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="X35">
-        <v>4.58</v>
-      </c>
-      <c r="Z35">
         <v>0.62</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G36">
         <v>5220</v>
       </c>
       <c r="H36" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O36">
         <v>48</v>
@@ -3701,64 +3671,64 @@
       <c r="P36" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="S36" t="s">
-        <v>30</v>
+      <c r="R36" t="s">
+        <v>25</v>
+      </c>
+      <c r="S36">
+        <v>4.6100000000000003</v>
       </c>
       <c r="T36">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U36">
+        <v>4.58</v>
       </c>
       <c r="V36">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="X36">
-        <v>4.58</v>
-      </c>
-      <c r="Z36">
         <v>0.62</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G37">
         <v>5220</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J37" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="M37" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="N37" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O37">
         <v>48</v>
@@ -3766,129 +3736,129 @@
       <c r="P37" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="S37" t="s">
-        <v>30</v>
+      <c r="R37" t="s">
+        <v>25</v>
+      </c>
+      <c r="S37">
+        <v>4.6100000000000003</v>
       </c>
       <c r="T37">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U37">
+        <v>4.58</v>
       </c>
       <c r="V37">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="X37">
-        <v>4.58</v>
-      </c>
-      <c r="Z37">
         <v>0.62</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G38">
         <v>5720</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O38" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P38" s="1">
         <v>0.61099999999999999</v>
       </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
       <c r="S38">
-        <v>1</v>
+        <v>4.45</v>
       </c>
       <c r="T38">
-        <v>4.45</v>
+        <v>0.83</v>
+      </c>
+      <c r="U38">
+        <v>4.55</v>
       </c>
       <c r="V38">
         <v>0.83</v>
       </c>
-      <c r="X38">
-        <v>4.55</v>
-      </c>
-      <c r="Z38">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G39">
         <v>5720</v>
       </c>
       <c r="H39" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I39" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O39">
         <v>54</v>
@@ -3896,64 +3866,64 @@
       <c r="P39" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="S39" t="s">
-        <v>30</v>
+      <c r="R39" t="s">
+        <v>25</v>
+      </c>
+      <c r="S39">
+        <v>4.45</v>
       </c>
       <c r="T39">
-        <v>4.45</v>
+        <v>0.83</v>
+      </c>
+      <c r="U39">
+        <v>4.55</v>
       </c>
       <c r="V39">
         <v>0.83</v>
       </c>
-      <c r="X39">
-        <v>4.55</v>
-      </c>
-      <c r="Z39">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G40">
         <v>5720</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I40" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J40" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L40" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M40" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N40" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O40">
         <v>54</v>
@@ -3961,129 +3931,129 @@
       <c r="P40" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="S40" t="s">
-        <v>30</v>
+      <c r="R40" t="s">
+        <v>25</v>
+      </c>
+      <c r="S40">
+        <v>4.45</v>
       </c>
       <c r="T40">
-        <v>4.45</v>
+        <v>0.83</v>
+      </c>
+      <c r="U40">
+        <v>4.55</v>
       </c>
       <c r="V40">
         <v>0.83</v>
       </c>
-      <c r="X40">
-        <v>4.55</v>
-      </c>
-      <c r="Z40">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G41">
         <v>5745</v>
       </c>
       <c r="H41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O41" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P41" s="1">
         <v>0.45</v>
       </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
       <c r="S41">
-        <v>1</v>
+        <v>4.78</v>
       </c>
       <c r="T41">
-        <v>4.78</v>
+        <v>0.42</v>
+      </c>
+      <c r="U41">
+        <v>4.8099999999999996</v>
       </c>
       <c r="V41">
-        <v>0.42</v>
-      </c>
-      <c r="X41">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="Z41">
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G42">
         <v>5745</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O42">
         <v>60</v>
@@ -4091,64 +4061,64 @@
       <c r="P42" s="1">
         <v>0.45</v>
       </c>
-      <c r="S42" t="s">
-        <v>30</v>
+      <c r="R42" t="s">
+        <v>25</v>
+      </c>
+      <c r="S42">
+        <v>4.78</v>
       </c>
       <c r="T42">
-        <v>4.78</v>
+        <v>0.42</v>
+      </c>
+      <c r="U42">
+        <v>4.8099999999999996</v>
       </c>
       <c r="V42">
-        <v>0.42</v>
-      </c>
-      <c r="X42">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="Z42">
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G43">
         <v>5745</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L43" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M43" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="N43" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O43">
         <v>60</v>
@@ -4156,129 +4126,129 @@
       <c r="P43" s="1">
         <v>0.45</v>
       </c>
-      <c r="S43" t="s">
-        <v>30</v>
+      <c r="R43" t="s">
+        <v>25</v>
+      </c>
+      <c r="S43">
+        <v>4.78</v>
       </c>
       <c r="T43">
-        <v>4.78</v>
+        <v>0.42</v>
+      </c>
+      <c r="U43">
+        <v>4.8099999999999996</v>
       </c>
       <c r="V43">
-        <v>0.42</v>
-      </c>
-      <c r="X43">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="Z43">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P44" s="1">
         <v>0.77800000000000002</v>
       </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
       <c r="S44">
-        <v>1</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="T44">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
+      </c>
+      <c r="U44">
+        <v>4.43</v>
       </c>
       <c r="V44">
-        <v>0.77</v>
-      </c>
-      <c r="X44">
-        <v>4.43</v>
-      </c>
-      <c r="Z44">
         <v>0.65</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>94</v>
+      </c>
+      <c r="H45" t="s">
         <v>35</v>
       </c>
-      <c r="F45" t="s">
-        <v>35</v>
-      </c>
-      <c r="G45" t="s">
-        <v>99</v>
-      </c>
-      <c r="H45" t="s">
-        <v>40</v>
-      </c>
       <c r="I45" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J45" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L45" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O45">
         <v>18</v>
@@ -4286,64 +4256,64 @@
       <c r="P45" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="S45" t="s">
-        <v>30</v>
+      <c r="R45" t="s">
+        <v>25</v>
+      </c>
+      <c r="S45">
+        <v>4.1399999999999997</v>
       </c>
       <c r="T45">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
+      </c>
+      <c r="U45">
+        <v>4.43</v>
       </c>
       <c r="V45">
-        <v>0.77</v>
-      </c>
-      <c r="X45">
-        <v>4.43</v>
-      </c>
-      <c r="Z45">
         <v>0.65</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46" t="s">
         <v>35</v>
       </c>
-      <c r="F46" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
+        <v>95</v>
+      </c>
+      <c r="J46" t="s">
+        <v>96</v>
+      </c>
+      <c r="K46" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" t="s">
+        <v>97</v>
+      </c>
+      <c r="M46" t="s">
+        <v>98</v>
+      </c>
+      <c r="N46" t="s">
         <v>99</v>
-      </c>
-      <c r="H46" t="s">
-        <v>40</v>
-      </c>
-      <c r="I46" t="s">
-        <v>100</v>
-      </c>
-      <c r="J46" t="s">
-        <v>101</v>
-      </c>
-      <c r="K46" t="s">
-        <v>30</v>
-      </c>
-      <c r="L46" t="s">
-        <v>102</v>
-      </c>
-      <c r="M46" t="s">
-        <v>103</v>
-      </c>
-      <c r="N46" t="s">
-        <v>104</v>
       </c>
       <c r="O46">
         <v>18</v>
@@ -4351,132 +4321,132 @@
       <c r="P46" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="S46" t="s">
-        <v>30</v>
+      <c r="R46" t="s">
+        <v>25</v>
+      </c>
+      <c r="S46">
+        <v>4.1399999999999997</v>
       </c>
       <c r="T46">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
+      </c>
+      <c r="U46">
+        <v>4.43</v>
       </c>
       <c r="V46">
-        <v>0.77</v>
-      </c>
-      <c r="X46">
-        <v>4.43</v>
-      </c>
-      <c r="Z46">
         <v>0.65</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I47" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P47" s="1">
         <v>0.53600000000000003</v>
       </c>
       <c r="Q47" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R47">
+        <v>1</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="T47">
-        <v>4.4000000000000004</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U47">
+        <v>4.53</v>
       </c>
       <c r="V47">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X47">
-        <v>4.53</v>
-      </c>
-      <c r="Z47">
         <v>0.83</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
+        <v>30</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>100</v>
+      </c>
+      <c r="H48" t="s">
         <v>35</v>
       </c>
-      <c r="F48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G48" t="s">
-        <v>105</v>
-      </c>
-      <c r="H48" t="s">
-        <v>40</v>
-      </c>
       <c r="I48" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J48" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O48">
         <v>28</v>
@@ -4485,66 +4455,66 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="Q48" t="s">
-        <v>33</v>
-      </c>
-      <c r="S48" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R48" t="s">
+        <v>25</v>
+      </c>
+      <c r="S48">
+        <v>4.4000000000000004</v>
       </c>
       <c r="T48">
-        <v>4.4000000000000004</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U48">
+        <v>4.53</v>
       </c>
       <c r="V48">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X48">
-        <v>4.53</v>
-      </c>
-      <c r="Z48">
         <v>0.83</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s">
+        <v>100</v>
+      </c>
+      <c r="H49" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
-        <v>35</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
+        <v>101</v>
+      </c>
+      <c r="J49" t="s">
+        <v>102</v>
+      </c>
+      <c r="K49" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" t="s">
+        <v>103</v>
+      </c>
+      <c r="M49" t="s">
+        <v>104</v>
+      </c>
+      <c r="N49" t="s">
         <v>105</v>
-      </c>
-      <c r="H49" t="s">
-        <v>40</v>
-      </c>
-      <c r="I49" t="s">
-        <v>106</v>
-      </c>
-      <c r="J49" t="s">
-        <v>107</v>
-      </c>
-      <c r="K49" t="s">
-        <v>30</v>
-      </c>
-      <c r="L49" t="s">
-        <v>108</v>
-      </c>
-      <c r="M49" t="s">
-        <v>109</v>
-      </c>
-      <c r="N49" t="s">
-        <v>110</v>
       </c>
       <c r="O49">
         <v>28</v>
@@ -4553,134 +4523,134 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="Q49" t="s">
+        <v>28</v>
+      </c>
+      <c r="R49" t="s">
+        <v>25</v>
+      </c>
+      <c r="S49">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="T49">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U49">
+        <v>4.53</v>
+      </c>
+      <c r="V49">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
         <v>33</v>
       </c>
-      <c r="S49" t="s">
-        <v>30</v>
-      </c>
-      <c r="T49">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="V49">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X49">
-        <v>4.53</v>
-      </c>
-      <c r="Z49">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>27</v>
-      </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" t="s">
-        <v>38</v>
-      </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P50" s="1">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q50" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
       </c>
       <c r="S50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
         <v>5</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
-      <c r="X50">
-        <v>5</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" t="s">
+        <v>30</v>
+      </c>
+      <c r="G51" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" t="s">
         <v>35</v>
       </c>
-      <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H51" t="s">
-        <v>40</v>
-      </c>
       <c r="I51" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J51" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O51">
         <v>13</v>
@@ -4689,66 +4659,66 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q51" t="s">
-        <v>33</v>
-      </c>
-      <c r="S51" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R51" t="s">
+        <v>25</v>
+      </c>
+      <c r="S51">
+        <v>5</v>
       </c>
       <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
         <v>5</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
-      <c r="X51">
-        <v>5</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" t="s">
         <v>35</v>
       </c>
-      <c r="F52" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
+        <v>107</v>
+      </c>
+      <c r="J52" t="s">
+        <v>108</v>
+      </c>
+      <c r="K52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>109</v>
+      </c>
+      <c r="M52" t="s">
+        <v>110</v>
+      </c>
+      <c r="N52" t="s">
         <v>111</v>
-      </c>
-      <c r="H52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I52" t="s">
-        <v>112</v>
-      </c>
-      <c r="J52" t="s">
-        <v>113</v>
-      </c>
-      <c r="K52" t="s">
-        <v>30</v>
-      </c>
-      <c r="L52" t="s">
-        <v>114</v>
-      </c>
-      <c r="M52" t="s">
-        <v>115</v>
-      </c>
-      <c r="N52" t="s">
-        <v>116</v>
       </c>
       <c r="O52">
         <v>13</v>
@@ -4757,131 +4727,131 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q52" t="s">
-        <v>33</v>
-      </c>
-      <c r="S52" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R52" t="s">
+        <v>25</v>
+      </c>
+      <c r="S52">
+        <v>5</v>
       </c>
       <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
         <v>5</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
-      <c r="X52">
-        <v>5</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G53">
         <v>5590</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I53" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O53" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P53" s="1">
         <v>0.56100000000000005</v>
       </c>
+      <c r="R53">
+        <v>2</v>
+      </c>
       <c r="S53">
-        <v>2</v>
+        <v>4.03</v>
       </c>
       <c r="T53">
-        <v>4.03</v>
+        <v>0.98</v>
+      </c>
+      <c r="U53">
+        <v>4.3600000000000003</v>
       </c>
       <c r="V53">
-        <v>0.98</v>
-      </c>
-      <c r="X53">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="Z53">
         <v>0.82</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G54">
         <v>5590</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J54" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K54" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L54" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M54" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O54">
         <v>63</v>
@@ -4889,64 +4859,64 @@
       <c r="P54" s="1">
         <v>0.55600000000000005</v>
       </c>
-      <c r="S54" t="s">
-        <v>30</v>
+      <c r="R54" t="s">
+        <v>25</v>
+      </c>
+      <c r="S54">
+        <v>4.29</v>
       </c>
       <c r="T54">
-        <v>4.29</v>
+        <v>0.79</v>
+      </c>
+      <c r="U54">
+        <v>4.51</v>
       </c>
       <c r="V54">
-        <v>0.79</v>
-      </c>
-      <c r="X54">
-        <v>4.51</v>
-      </c>
-      <c r="Z54">
         <v>0.66</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G55">
         <v>5590</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K55" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M55" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N55" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="O55">
         <v>63</v>
@@ -4954,64 +4924,64 @@
       <c r="P55" s="1">
         <v>0.55600000000000005</v>
       </c>
-      <c r="S55" t="s">
-        <v>30</v>
+      <c r="R55" t="s">
+        <v>25</v>
+      </c>
+      <c r="S55">
+        <v>4.29</v>
       </c>
       <c r="T55">
-        <v>4.29</v>
+        <v>0.79</v>
+      </c>
+      <c r="U55">
+        <v>4.51</v>
       </c>
       <c r="V55">
-        <v>0.79</v>
-      </c>
-      <c r="X55">
-        <v>4.51</v>
-      </c>
-      <c r="Z55">
         <v>0.66</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G56">
         <v>5590</v>
       </c>
       <c r="H56" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I56" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J56" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K56" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L56" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M56" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O56">
         <v>60</v>
@@ -5019,64 +4989,64 @@
       <c r="P56" s="1">
         <v>0.56699999999999995</v>
       </c>
-      <c r="S56" t="s">
-        <v>30</v>
+      <c r="R56" t="s">
+        <v>25</v>
+      </c>
+      <c r="S56">
+        <v>3.76</v>
       </c>
       <c r="T56">
-        <v>3.76</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U56">
+        <v>4.21</v>
       </c>
       <c r="V56">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X56">
-        <v>4.21</v>
-      </c>
-      <c r="Z56">
         <v>0.95</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G57">
         <v>5590</v>
       </c>
       <c r="H57" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I57" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J57" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K57" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="M57" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N57" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="O57">
         <v>60</v>
@@ -5084,129 +5054,129 @@
       <c r="P57" s="1">
         <v>0.56699999999999995</v>
       </c>
-      <c r="S57" t="s">
-        <v>30</v>
+      <c r="R57" t="s">
+        <v>25</v>
+      </c>
+      <c r="S57">
+        <v>3.76</v>
       </c>
       <c r="T57">
-        <v>3.76</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U57">
+        <v>4.21</v>
       </c>
       <c r="V57">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X57">
-        <v>4.21</v>
-      </c>
-      <c r="Z57">
         <v>0.95</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G58">
         <v>5120</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O58" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P58" s="1">
         <v>0.61499999999999999</v>
       </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
       <c r="S58">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T58">
-        <v>4.63</v>
+        <v>0.62</v>
+      </c>
+      <c r="U58">
+        <v>4.88</v>
       </c>
       <c r="V58">
-        <v>0.62</v>
-      </c>
-      <c r="X58">
-        <v>4.88</v>
-      </c>
-      <c r="Z58">
         <v>0.34</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G59">
         <v>5120</v>
       </c>
       <c r="H59" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J59" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K59" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L59" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M59" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O59">
         <v>26</v>
@@ -5214,64 +5184,64 @@
       <c r="P59" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="S59" t="s">
-        <v>30</v>
+      <c r="R59" t="s">
+        <v>25</v>
+      </c>
+      <c r="S59">
+        <v>4.63</v>
       </c>
       <c r="T59">
-        <v>4.63</v>
+        <v>0.62</v>
+      </c>
+      <c r="U59">
+        <v>4.88</v>
       </c>
       <c r="V59">
-        <v>0.62</v>
-      </c>
-      <c r="X59">
-        <v>4.88</v>
-      </c>
-      <c r="Z59">
         <v>0.34</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G60">
         <v>5120</v>
       </c>
       <c r="H60" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J60" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K60" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L60" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="M60" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="N60" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="O60">
         <v>26</v>
@@ -5279,60 +5249,60 @@
       <c r="P60" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="S60" t="s">
-        <v>30</v>
+      <c r="R60" t="s">
+        <v>25</v>
+      </c>
+      <c r="S60">
+        <v>4.63</v>
       </c>
       <c r="T60">
-        <v>4.63</v>
+        <v>0.62</v>
+      </c>
+      <c r="U60">
+        <v>4.88</v>
       </c>
       <c r="V60">
-        <v>0.62</v>
-      </c>
-      <c r="X60">
-        <v>4.88</v>
-      </c>
-      <c r="Z60">
         <v>0.34</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
@@ -5346,6 +5316,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -5594,15 +5573,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5615,13 +5585,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EDC754-5AC1-4749-98EC-DCBC89EF2339}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F10AEF6-FF50-4564-ABC5-C00E90F498A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F10AEF6-FF50-4564-ABC5-C00E90F498A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EDC754-5AC1-4749-98EC-DCBC89EF2339}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377033B3-E736-4098-B9D1-4FB40012ED70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377033B3-E736-4098-B9D1-4FB40012ED70}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/bm-w26.xlsx
+++ b/bm-w26.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{139F8E74-0F73-4C21-B08E-EB1095D47A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43F00831-AD35-49D2-8329-31B9C5D5CD94}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6246EF33-5269-4A79-853D-EE8FFEBC5DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFED0C5F-B0F5-409D-A387-6DF1DA8B8075}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{80BE6F33-D422-4D14-BE1C-AADC7C177704}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFF204E3-9B84-4E55-94D5-F8C645A41361}"/>
   </bookViews>
   <sheets>
-    <sheet name="School_Term_Summary_Report-SBM-" sheetId="1" r:id="rId1"/>
+    <sheet name="bm-w26" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="144">
   <si>
     <t>Academic Year</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Low Response Rate Indicator</t>
   </si>
   <si>
+    <t>Response Rate (Adjusted)</t>
+  </si>
+  <si>
     <t>No. of Sections Evaluated</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
     <t>MARK</t>
   </si>
   <si>
+    <t>SBMT</t>
+  </si>
+  <si>
     <t>Course</t>
   </si>
   <si>
@@ -395,6 +401,33 @@
   </si>
   <si>
     <t>mkjiewen</t>
+  </si>
+  <si>
+    <t>25-26-Winter-SBMT-5300</t>
+  </si>
+  <si>
+    <t>25-26-Winter-SBMT-5300-L1</t>
+  </si>
+  <si>
+    <t>25-26-WINTER-SBMT-5300-L1-Instructor</t>
+  </si>
+  <si>
+    <t>DORAN, Christopher</t>
+  </si>
+  <si>
+    <t>cjsd</t>
+  </si>
+  <si>
+    <t>NASON, Stephen William</t>
+  </si>
+  <si>
+    <t>mnsnason</t>
+  </si>
+  <si>
+    <t>SALVACRUZ, Joseph</t>
+  </si>
+  <si>
+    <t>mkjcs</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -1280,11 +1313,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3365DD5F-5537-4265-958E-1E14DD797E1B}">
-  <dimension ref="A1:V72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{595447D4-B5E5-44C0-A029-72E389C850E9}">
+  <dimension ref="A1:W78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,581 +1384,581 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="1">
-        <v>0.40699999999999997</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="Q2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S2">
+        <v>19</v>
+      </c>
+      <c r="T2">
         <v>4.42</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>0.79</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>4.59</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3">
+        <v>29</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>4.5599999999999996</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>0.73</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>4.4400000000000004</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>1.01</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="1">
         <v>0.43</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>2</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>4.6900000000000004</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0.5</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>4.74</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="1">
         <v>0.38400000000000001</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>12</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>4.4400000000000004</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>0.76</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>4.55</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>0.68</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1">
         <v>0.56100000000000005</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>2</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>4.03</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.98</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>4.3600000000000003</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>0.82</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>1</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>4.63</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>0.62</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>4.88</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>0.34</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>5100</v>
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" s="1">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="Q8" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>4.32</v>
+      </c>
+      <c r="U8">
+        <v>0.9</v>
+      </c>
+      <c r="V8">
+        <v>4.79</v>
+      </c>
+      <c r="W8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="T8">
-        <v>0.73</v>
-      </c>
-      <c r="U8">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9">
         <v>5100</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9">
-        <v>51</v>
+        <v>26</v>
+      </c>
+      <c r="O9" t="s">
+        <v>26</v>
       </c>
       <c r="P9" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q9" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="U9">
+        <v>0.73</v>
+      </c>
+      <c r="V9">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="R9" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="T9">
-        <v>0.73</v>
-      </c>
-      <c r="U9">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10">
         <v>5100</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="O10">
         <v>51</v>
@@ -1934,196 +1967,199 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="Q10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="U10">
+        <v>0.73</v>
+      </c>
+      <c r="V10">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
         <v>28</v>
       </c>
-      <c r="R10" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10">
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11">
+        <v>5100</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11">
+        <v>51</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>29</v>
+      </c>
+      <c r="S11" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11">
         <v>4.5599999999999996</v>
       </c>
-      <c r="T10">
+      <c r="U11">
         <v>0.73</v>
       </c>
-      <c r="U10">
+      <c r="V11">
         <v>4.4400000000000004</v>
       </c>
-      <c r="V10">
+      <c r="W11">
         <v>1.01</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11">
-        <v>5341</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0.35899999999999999</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>4.79</v>
-      </c>
-      <c r="T11">
-        <v>0.42</v>
-      </c>
-      <c r="U11">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="V11">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>5341</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12">
-        <v>78</v>
+        <v>26</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
       </c>
       <c r="P12" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="R12" t="s">
-        <v>25</v>
-      </c>
       <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
         <v>4.79</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0.42</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>4.8600000000000003</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>5341</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="O13">
         <v>78</v>
@@ -2131,194 +2167,194 @@
       <c r="P13" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="R13" t="s">
-        <v>25</v>
-      </c>
-      <c r="S13">
+      <c r="S13" t="s">
+        <v>26</v>
+      </c>
+      <c r="T13">
         <v>4.79</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>0.42</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>4.8600000000000003</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14">
-        <v>5347</v>
+        <v>5341</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" t="s">
         <v>46</v>
       </c>
-      <c r="J14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>25</v>
-      </c>
       <c r="N14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" t="s">
-        <v>25</v>
+        <v>47</v>
+      </c>
+      <c r="O14">
+        <v>78</v>
       </c>
       <c r="P14" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
-        <v>4.63</v>
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="S14" t="s">
+        <v>26</v>
       </c>
       <c r="T14">
-        <v>0.54</v>
+        <v>4.79</v>
       </c>
       <c r="U14">
-        <v>4.6500000000000004</v>
+        <v>0.42</v>
       </c>
       <c r="V14">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="W14">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15">
         <v>5347</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15">
-        <v>80</v>
+        <v>26</v>
+      </c>
+      <c r="O15" t="s">
+        <v>26</v>
       </c>
       <c r="P15" s="1">
         <v>0.5</v>
       </c>
-      <c r="R15" t="s">
-        <v>25</v>
-      </c>
       <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
         <v>4.63</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>0.54</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>4.6500000000000004</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>0.53</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16">
         <v>5347</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="O16">
         <v>80</v>
@@ -2326,34 +2362,34 @@
       <c r="P16" s="1">
         <v>0.5</v>
       </c>
-      <c r="R16" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16">
+      <c r="S16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16">
         <v>4.63</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>0.54</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>4.6500000000000004</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>0.53</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -2362,164 +2398,161 @@
         <v>30</v>
       </c>
       <c r="G17">
-        <v>1090</v>
+        <v>5347</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" t="s">
         <v>51</v>
       </c>
-      <c r="J17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" t="s">
-        <v>25</v>
-      </c>
       <c r="N17" t="s">
-        <v>25</v>
-      </c>
-      <c r="O17" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="O17">
+        <v>80</v>
       </c>
       <c r="P17" s="1">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <v>3.95</v>
+        <v>0.5</v>
+      </c>
+      <c r="S17" t="s">
+        <v>26</v>
       </c>
       <c r="T17">
-        <v>0.97</v>
+        <v>4.63</v>
       </c>
       <c r="U17">
-        <v>4.32</v>
+        <v>0.54</v>
       </c>
       <c r="V17">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="W17">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18">
         <v>1090</v>
       </c>
       <c r="H18" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18">
-        <v>78</v>
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
+        <v>26</v>
       </c>
       <c r="P18" s="1">
         <v>0.24399999999999999</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
-      </c>
-      <c r="R18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
         <v>3.95</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>0.97</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>4.32</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G19">
         <v>1090</v>
       </c>
       <c r="H19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="O19">
         <v>78</v>
@@ -2528,202 +2561,202 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R19" t="s">
-        <v>25</v>
-      </c>
-      <c r="S19">
+        <v>29</v>
+      </c>
+      <c r="S19" t="s">
+        <v>26</v>
+      </c>
+      <c r="T19">
         <v>3.95</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>0.97</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>4.32</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>0.75</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G20">
-        <v>1380</v>
+        <v>1090</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" t="s">
         <v>56</v>
       </c>
-      <c r="J20" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" t="s">
-        <v>25</v>
-      </c>
       <c r="N20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="O20">
+        <v>78</v>
       </c>
       <c r="P20" s="1">
-        <v>0.27800000000000002</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>4.41</v>
+        <v>29</v>
+      </c>
+      <c r="S20" t="s">
+        <v>26</v>
       </c>
       <c r="T20">
-        <v>0.59</v>
+        <v>3.95</v>
       </c>
       <c r="U20">
-        <v>4.55</v>
+        <v>0.97</v>
       </c>
       <c r="V20">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.32</v>
+      </c>
+      <c r="W20">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G21">
         <v>1380</v>
       </c>
       <c r="H21" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J21" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21">
-        <v>79</v>
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
+        <v>26</v>
       </c>
       <c r="P21" s="1">
         <v>0.27800000000000002</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
-      </c>
-      <c r="R21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
         <v>4.41</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>0.59</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>4.55</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22">
         <v>1380</v>
       </c>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L22" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="O22">
         <v>79</v>
@@ -2732,196 +2765,199 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
-      </c>
-      <c r="R22" t="s">
-        <v>25</v>
-      </c>
-      <c r="S22">
+        <v>29</v>
+      </c>
+      <c r="S22" t="s">
+        <v>26</v>
+      </c>
+      <c r="T22">
         <v>4.41</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>0.59</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>4.55</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>0.6</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>1700</v>
+        <v>1380</v>
       </c>
       <c r="H23" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" t="s">
         <v>61</v>
       </c>
-      <c r="J23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" t="s">
-        <v>25</v>
-      </c>
       <c r="N23" t="s">
-        <v>25</v>
-      </c>
-      <c r="O23" t="s">
-        <v>25</v>
+        <v>62</v>
+      </c>
+      <c r="O23">
+        <v>79</v>
       </c>
       <c r="P23" s="1">
-        <v>0.34799999999999998</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23">
-        <v>4.43</v>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>29</v>
+      </c>
+      <c r="S23" t="s">
+        <v>26</v>
       </c>
       <c r="T23">
-        <v>0.7</v>
+        <v>4.41</v>
       </c>
       <c r="U23">
-        <v>4.57</v>
+        <v>0.59</v>
       </c>
       <c r="V23">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.55</v>
+      </c>
+      <c r="W23">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G24">
         <v>1700</v>
       </c>
       <c r="H24" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>25</v>
-      </c>
-      <c r="O24">
-        <v>198</v>
+        <v>26</v>
+      </c>
+      <c r="O24" t="s">
+        <v>26</v>
       </c>
       <c r="P24" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="R24" t="s">
-        <v>25</v>
-      </c>
       <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
         <v>4.43</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>0.7</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>4.57</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>0.63</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25">
         <v>1700</v>
       </c>
       <c r="H25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O25">
         <v>198</v>
@@ -2929,200 +2965,197 @@
       <c r="P25" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="R25" t="s">
-        <v>25</v>
-      </c>
-      <c r="S25">
+      <c r="S25" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25">
         <v>4.43</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>0.7</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>4.57</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>0.63</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26">
-        <v>2400</v>
+        <v>1700</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
         <v>66</v>
       </c>
-      <c r="J26" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" t="s">
-        <v>25</v>
-      </c>
       <c r="N26" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" t="s">
-        <v>25</v>
+        <v>67</v>
+      </c>
+      <c r="O26">
+        <v>198</v>
       </c>
       <c r="P26" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>28</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>4.07</v>
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="S26" t="s">
+        <v>26</v>
       </c>
       <c r="T26">
-        <v>0.9</v>
+        <v>4.43</v>
       </c>
       <c r="U26">
-        <v>4.3600000000000003</v>
+        <v>0.7</v>
       </c>
       <c r="V26">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.57</v>
+      </c>
+      <c r="W26">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G27">
         <v>2400</v>
       </c>
       <c r="H27" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J27" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27">
-        <v>100</v>
+        <v>26</v>
+      </c>
+      <c r="O27" t="s">
+        <v>26</v>
       </c>
       <c r="P27" s="1">
         <v>0.28000000000000003</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
-      </c>
-      <c r="R27" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
         <v>4.07</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>0.9</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>4.3600000000000003</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G28">
         <v>2400</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -3131,202 +3164,202 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q28" t="s">
-        <v>28</v>
-      </c>
-      <c r="R28" t="s">
-        <v>25</v>
-      </c>
-      <c r="S28">
+        <v>29</v>
+      </c>
+      <c r="S28" t="s">
+        <v>26</v>
+      </c>
+      <c r="T28">
         <v>4.07</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>0.9</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>4.3600000000000003</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>0.83</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G29">
-        <v>4010</v>
+        <v>2400</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I29" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" t="s">
+        <v>70</v>
+      </c>
+      <c r="M29" t="s">
         <v>71</v>
       </c>
-      <c r="J29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" t="s">
-        <v>25</v>
-      </c>
       <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="O29">
+        <v>100</v>
       </c>
       <c r="P29" s="1">
-        <v>0.435</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>4.9000000000000004</v>
+        <v>29</v>
+      </c>
+      <c r="S29" t="s">
+        <v>26</v>
       </c>
       <c r="T29">
-        <v>0.32</v>
+        <v>4.07</v>
       </c>
       <c r="U29">
-        <v>4.9000000000000004</v>
+        <v>0.9</v>
       </c>
       <c r="V29">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="W29">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G30">
         <v>4010</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="K30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>25</v>
-      </c>
-      <c r="O30">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="O30" t="s">
+        <v>26</v>
       </c>
       <c r="P30" s="1">
         <v>0.435</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
-      </c>
-      <c r="R30" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S30">
+        <v>1</v>
+      </c>
+      <c r="T30">
         <v>4.9000000000000004</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>0.32</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>4.9000000000000004</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>0.32</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G31">
         <v>4010</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="O31">
         <v>23</v>
@@ -3335,202 +3368,202 @@
         <v>0.435</v>
       </c>
       <c r="Q31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S31">
+        <v>29</v>
+      </c>
+      <c r="S31" t="s">
+        <v>26</v>
+      </c>
+      <c r="T31">
         <v>4.9000000000000004</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>0.32</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>4.9000000000000004</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>0.32</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G32">
-        <v>4740</v>
+        <v>4010</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I32" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" t="s">
+        <v>75</v>
+      </c>
+      <c r="M32" t="s">
         <v>76</v>
       </c>
-      <c r="J32" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>25</v>
-      </c>
       <c r="N32" t="s">
-        <v>25</v>
-      </c>
-      <c r="O32" t="s">
-        <v>25</v>
+        <v>77</v>
+      </c>
+      <c r="O32">
+        <v>23</v>
       </c>
       <c r="P32" s="1">
-        <v>0.36399999999999999</v>
+        <v>0.435</v>
       </c>
       <c r="Q32" t="s">
-        <v>28</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="S32" t="s">
+        <v>26</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="U32">
-        <v>4.5</v>
+        <v>0.32</v>
       </c>
       <c r="V32">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W32">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G33">
         <v>4740</v>
       </c>
       <c r="H33" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>25</v>
-      </c>
-      <c r="O33">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
+        <v>26</v>
       </c>
       <c r="P33" s="1">
         <v>0.36399999999999999</v>
       </c>
       <c r="Q33" t="s">
-        <v>28</v>
-      </c>
-      <c r="R33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
         <v>5</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>0</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>4.5</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>0.76</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G34">
         <v>4740</v>
       </c>
       <c r="H34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="M34" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="O34">
         <v>22</v>
@@ -3539,196 +3572,199 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
-      </c>
-      <c r="R34" t="s">
-        <v>25</v>
-      </c>
-      <c r="S34">
+        <v>29</v>
+      </c>
+      <c r="S34" t="s">
+        <v>26</v>
+      </c>
+      <c r="T34">
         <v>5</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>0</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>4.5</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>0.76</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35">
+        <v>4740</v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" t="s">
+        <v>80</v>
+      </c>
+      <c r="M35" t="s">
+        <v>81</v>
+      </c>
+      <c r="N35" t="s">
+        <v>82</v>
+      </c>
+      <c r="O35">
         <v>22</v>
       </c>
-      <c r="B35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35">
-        <v>5220</v>
-      </c>
-      <c r="H35" t="s">
-        <v>25</v>
-      </c>
-      <c r="I35" t="s">
-        <v>81</v>
-      </c>
-      <c r="J35" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" t="s">
-        <v>25</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" t="s">
-        <v>25</v>
-      </c>
-      <c r="N35" t="s">
-        <v>25</v>
-      </c>
-      <c r="O35" t="s">
-        <v>25</v>
-      </c>
       <c r="P35" s="1">
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="S35">
-        <v>4.6100000000000003</v>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>29</v>
+      </c>
+      <c r="S35" t="s">
+        <v>26</v>
       </c>
       <c r="T35">
-        <v>0.56000000000000005</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.5</v>
+      </c>
+      <c r="W35">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G36">
         <v>5220</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J36" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36">
-        <v>48</v>
+        <v>26</v>
+      </c>
+      <c r="O36" t="s">
+        <v>26</v>
       </c>
       <c r="P36" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="R36" t="s">
-        <v>25</v>
-      </c>
       <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="T36">
         <v>4.6100000000000003</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>0.56000000000000005</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>4.58</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>0.62</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G37">
         <v>5220</v>
       </c>
       <c r="H37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L37" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="O37">
         <v>48</v>
@@ -3736,194 +3772,194 @@
       <c r="P37" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="R37" t="s">
-        <v>25</v>
-      </c>
-      <c r="S37">
+      <c r="S37" t="s">
+        <v>26</v>
+      </c>
+      <c r="T37">
         <v>4.6100000000000003</v>
       </c>
-      <c r="T37">
+      <c r="U37">
         <v>0.56000000000000005</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>4.58</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <v>0.62</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G38">
-        <v>5720</v>
+        <v>5220</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I38" t="s">
+        <v>83</v>
+      </c>
+      <c r="J38" t="s">
+        <v>84</v>
+      </c>
+      <c r="K38" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" t="s">
+        <v>85</v>
+      </c>
+      <c r="M38" t="s">
         <v>86</v>
       </c>
-      <c r="J38" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" t="s">
-        <v>25</v>
-      </c>
       <c r="N38" t="s">
-        <v>25</v>
-      </c>
-      <c r="O38" t="s">
-        <v>25</v>
+        <v>87</v>
+      </c>
+      <c r="O38">
+        <v>48</v>
       </c>
       <c r="P38" s="1">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38">
-        <v>4.45</v>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="S38" t="s">
+        <v>26</v>
       </c>
       <c r="T38">
-        <v>0.83</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="U38">
-        <v>4.55</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="V38">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.58</v>
+      </c>
+      <c r="W38">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G39">
         <v>5720</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J39" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>25</v>
-      </c>
-      <c r="O39">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="O39" t="s">
+        <v>26</v>
       </c>
       <c r="P39" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="R39" t="s">
-        <v>25</v>
-      </c>
       <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39">
         <v>4.45</v>
       </c>
-      <c r="T39">
+      <c r="U39">
         <v>0.83</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>4.55</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <v>0.83</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G40">
         <v>5720</v>
       </c>
       <c r="H40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L40" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="M40" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O40">
         <v>54</v>
@@ -3931,194 +3967,194 @@
       <c r="P40" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="R40" t="s">
-        <v>25</v>
-      </c>
-      <c r="S40">
+      <c r="S40" t="s">
+        <v>26</v>
+      </c>
+      <c r="T40">
         <v>4.45</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>0.83</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>4.55</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <v>0.83</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41">
-        <v>5745</v>
+        <v>5720</v>
       </c>
       <c r="H41" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41" t="s">
         <v>89</v>
       </c>
-      <c r="J41" t="s">
-        <v>25</v>
-      </c>
       <c r="K41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="M41" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="N41" t="s">
-        <v>25</v>
-      </c>
-      <c r="O41" t="s">
-        <v>25</v>
+        <v>67</v>
+      </c>
+      <c r="O41">
+        <v>54</v>
       </c>
       <c r="P41" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41">
-        <v>4.78</v>
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="S41" t="s">
+        <v>26</v>
       </c>
       <c r="T41">
-        <v>0.42</v>
+        <v>4.45</v>
       </c>
       <c r="U41">
-        <v>4.8099999999999996</v>
+        <v>0.83</v>
       </c>
       <c r="V41">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.55</v>
+      </c>
+      <c r="W41">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G42">
         <v>5745</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J42" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>25</v>
-      </c>
-      <c r="O42">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="O42" t="s">
+        <v>26</v>
       </c>
       <c r="P42" s="1">
         <v>0.45</v>
       </c>
-      <c r="R42" t="s">
-        <v>25</v>
-      </c>
       <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42">
         <v>4.78</v>
       </c>
-      <c r="T42">
+      <c r="U42">
         <v>0.42</v>
       </c>
-      <c r="U42">
+      <c r="V42">
         <v>4.8099999999999996</v>
       </c>
-      <c r="V42">
+      <c r="W42">
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G43">
         <v>5745</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L43" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="O43">
         <v>60</v>
@@ -4126,194 +4162,194 @@
       <c r="P43" s="1">
         <v>0.45</v>
       </c>
-      <c r="R43" t="s">
-        <v>25</v>
-      </c>
-      <c r="S43">
+      <c r="S43" t="s">
+        <v>26</v>
+      </c>
+      <c r="T43">
         <v>4.78</v>
       </c>
-      <c r="T43">
+      <c r="U43">
         <v>0.42</v>
       </c>
-      <c r="U43">
+      <c r="V43">
         <v>4.8099999999999996</v>
       </c>
-      <c r="V43">
+      <c r="W43">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44">
+        <v>5745</v>
+      </c>
+      <c r="H44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44" t="s">
+        <v>92</v>
+      </c>
+      <c r="K44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44" t="s">
+        <v>93</v>
+      </c>
+      <c r="M44" t="s">
         <v>94</v>
       </c>
-      <c r="H44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="N44" t="s">
         <v>95</v>
       </c>
-      <c r="J44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" t="s">
-        <v>25</v>
-      </c>
-      <c r="N44" t="s">
-        <v>25</v>
-      </c>
-      <c r="O44" t="s">
-        <v>25</v>
+      <c r="O44">
+        <v>60</v>
       </c>
       <c r="P44" s="1">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="R44">
-        <v>1</v>
-      </c>
-      <c r="S44">
-        <v>4.1399999999999997</v>
+        <v>0.45</v>
+      </c>
+      <c r="S44" t="s">
+        <v>26</v>
       </c>
       <c r="T44">
-        <v>0.77</v>
+        <v>4.78</v>
       </c>
       <c r="U44">
-        <v>4.43</v>
+        <v>0.42</v>
       </c>
       <c r="V44">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="W44">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J45" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>25</v>
-      </c>
-      <c r="O45">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="O45" t="s">
+        <v>26</v>
       </c>
       <c r="P45" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="R45" t="s">
-        <v>25</v>
-      </c>
       <c r="S45">
+        <v>1</v>
+      </c>
+      <c r="T45">
         <v>4.1399999999999997</v>
       </c>
-      <c r="T45">
+      <c r="U45">
         <v>0.77</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <v>4.43</v>
       </c>
-      <c r="V45">
+      <c r="W45">
         <v>0.65</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
+        <v>96</v>
+      </c>
+      <c r="H46" t="s">
         <v>37</v>
       </c>
-      <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" t="s">
-        <v>30</v>
-      </c>
-      <c r="G46" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" t="s">
-        <v>35</v>
-      </c>
       <c r="I46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L46" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="O46">
         <v>18</v>
@@ -4321,200 +4357,197 @@
       <c r="P46" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="R46" t="s">
-        <v>25</v>
-      </c>
-      <c r="S46">
+      <c r="S46" t="s">
+        <v>26</v>
+      </c>
+      <c r="T46">
         <v>4.1399999999999997</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <v>0.77</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>4.43</v>
       </c>
-      <c r="V46">
+      <c r="W46">
         <v>0.65</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G47" t="s">
+        <v>96</v>
+      </c>
+      <c r="H47" t="s">
+        <v>37</v>
+      </c>
+      <c r="I47" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" t="s">
+        <v>98</v>
+      </c>
+      <c r="K47" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" t="s">
+        <v>99</v>
+      </c>
+      <c r="M47" t="s">
         <v>100</v>
       </c>
-      <c r="H47" t="s">
-        <v>25</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="N47" t="s">
         <v>101</v>
       </c>
-      <c r="J47" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" t="s">
-        <v>25</v>
-      </c>
-      <c r="L47" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" t="s">
-        <v>25</v>
-      </c>
-      <c r="N47" t="s">
-        <v>25</v>
-      </c>
-      <c r="O47" t="s">
-        <v>25</v>
+      <c r="O47">
+        <v>18</v>
       </c>
       <c r="P47" s="1">
-        <v>0.53600000000000003</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>28</v>
-      </c>
-      <c r="R47">
-        <v>1</v>
-      </c>
-      <c r="S47">
-        <v>4.4000000000000004</v>
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="S47" t="s">
+        <v>26</v>
       </c>
       <c r="T47">
-        <v>1.1200000000000001</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="U47">
-        <v>4.53</v>
+        <v>0.77</v>
       </c>
       <c r="V47">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.43</v>
+      </c>
+      <c r="W47">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J48" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>25</v>
-      </c>
-      <c r="O48">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="O48" t="s">
+        <v>26</v>
       </c>
       <c r="P48" s="1">
         <v>0.53600000000000003</v>
       </c>
       <c r="Q48" t="s">
-        <v>28</v>
-      </c>
-      <c r="R48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S48">
+        <v>1</v>
+      </c>
+      <c r="T48">
         <v>4.4000000000000004</v>
       </c>
-      <c r="T48">
+      <c r="U48">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <v>4.53</v>
       </c>
-      <c r="V48">
+      <c r="W48">
         <v>0.83</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
+        <v>102</v>
+      </c>
+      <c r="H49" t="s">
         <v>37</v>
       </c>
-      <c r="D49" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" t="s">
-        <v>100</v>
-      </c>
-      <c r="H49" t="s">
-        <v>35</v>
-      </c>
       <c r="I49" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J49" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L49" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="N49" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="O49">
         <v>28</v>
@@ -4523,202 +4556,202 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="Q49" t="s">
+        <v>29</v>
+      </c>
+      <c r="S49" t="s">
+        <v>26</v>
+      </c>
+      <c r="T49">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U49">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="V49">
+        <v>4.53</v>
+      </c>
+      <c r="W49">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>102</v>
+      </c>
+      <c r="H50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" t="s">
+        <v>103</v>
+      </c>
+      <c r="J50" t="s">
+        <v>104</v>
+      </c>
+      <c r="K50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" t="s">
+        <v>105</v>
+      </c>
+      <c r="M50" t="s">
+        <v>106</v>
+      </c>
+      <c r="N50" t="s">
+        <v>107</v>
+      </c>
+      <c r="O50">
         <v>28</v>
       </c>
-      <c r="R49" t="s">
-        <v>25</v>
-      </c>
-      <c r="S49">
+      <c r="P50" s="1">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>29</v>
+      </c>
+      <c r="S50" t="s">
+        <v>26</v>
+      </c>
+      <c r="T50">
         <v>4.4000000000000004</v>
       </c>
-      <c r="T49">
+      <c r="U50">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U49">
+      <c r="V50">
         <v>4.53</v>
       </c>
-      <c r="V49">
+      <c r="W50">
         <v>0.83</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" t="s">
-        <v>106</v>
-      </c>
-      <c r="H50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I50" t="s">
-        <v>107</v>
-      </c>
-      <c r="J50" t="s">
-        <v>25</v>
-      </c>
-      <c r="K50" t="s">
-        <v>25</v>
-      </c>
-      <c r="L50" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" t="s">
-        <v>25</v>
-      </c>
-      <c r="N50" t="s">
-        <v>25</v>
-      </c>
-      <c r="O50" t="s">
-        <v>25</v>
-      </c>
-      <c r="P50" s="1">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>28</v>
-      </c>
-      <c r="R50">
-        <v>1</v>
-      </c>
-      <c r="S50">
-        <v>5</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>5</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G51" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I51" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J51" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>25</v>
-      </c>
-      <c r="O51">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="O51" t="s">
+        <v>26</v>
       </c>
       <c r="P51" s="1">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
-      </c>
-      <c r="R51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S51">
+        <v>1</v>
+      </c>
+      <c r="T51">
         <v>5</v>
       </c>
-      <c r="T51">
+      <c r="U51">
         <v>0</v>
       </c>
-      <c r="U51">
+      <c r="V51">
         <v>5</v>
       </c>
-      <c r="V51">
+      <c r="W51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" t="s">
+        <v>108</v>
+      </c>
+      <c r="H52" t="s">
         <v>37</v>
       </c>
-      <c r="D52" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" t="s">
-        <v>35</v>
-      </c>
       <c r="I52" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J52" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L52" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="O52">
         <v>13</v>
@@ -4727,36 +4760,36 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R52" t="s">
-        <v>25</v>
-      </c>
-      <c r="S52">
+        <v>29</v>
+      </c>
+      <c r="S52" t="s">
+        <v>26</v>
+      </c>
+      <c r="T52">
         <v>5</v>
       </c>
-      <c r="T52">
+      <c r="U52">
         <v>0</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <v>5</v>
       </c>
-      <c r="V52">
+      <c r="W52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
@@ -4764,159 +4797,162 @@
       <c r="F53" t="s">
         <v>31</v>
       </c>
-      <c r="G53">
-        <v>5590</v>
+      <c r="G53" t="s">
+        <v>108</v>
       </c>
       <c r="H53" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I53" t="s">
+        <v>109</v>
+      </c>
+      <c r="J53" t="s">
+        <v>110</v>
+      </c>
+      <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" t="s">
         <v>112</v>
       </c>
-      <c r="J53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L53" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" t="s">
-        <v>25</v>
-      </c>
       <c r="N53" t="s">
-        <v>25</v>
-      </c>
-      <c r="O53" t="s">
-        <v>25</v>
+        <v>113</v>
+      </c>
+      <c r="O53">
+        <v>13</v>
       </c>
       <c r="P53" s="1">
-        <v>0.56100000000000005</v>
-      </c>
-      <c r="R53">
-        <v>2</v>
-      </c>
-      <c r="S53">
-        <v>4.03</v>
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>29</v>
+      </c>
+      <c r="S53" t="s">
+        <v>26</v>
       </c>
       <c r="T53">
-        <v>0.98</v>
+        <v>5</v>
       </c>
       <c r="U53">
-        <v>4.3600000000000003</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G54">
         <v>5590</v>
       </c>
       <c r="H54" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J54" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>25</v>
-      </c>
-      <c r="O54">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="O54" t="s">
+        <v>26</v>
       </c>
       <c r="P54" s="1">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="R54" t="s">
-        <v>25</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="S54">
-        <v>4.29</v>
+        <v>2</v>
       </c>
       <c r="T54">
-        <v>0.79</v>
+        <v>4.03</v>
       </c>
       <c r="U54">
-        <v>4.51</v>
+        <v>0.98</v>
       </c>
       <c r="V54">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="W54">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55">
         <v>5590</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="M55" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="N55" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="O55">
         <v>63</v>
@@ -4924,129 +4960,129 @@
       <c r="P55" s="1">
         <v>0.55600000000000005</v>
       </c>
-      <c r="R55" t="s">
-        <v>25</v>
-      </c>
-      <c r="S55">
+      <c r="S55" t="s">
+        <v>26</v>
+      </c>
+      <c r="T55">
         <v>4.29</v>
       </c>
-      <c r="T55">
+      <c r="U55">
         <v>0.79</v>
       </c>
-      <c r="U55">
+      <c r="V55">
         <v>4.51</v>
       </c>
-      <c r="V55">
+      <c r="W55">
         <v>0.66</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G56">
         <v>5590</v>
       </c>
       <c r="H56" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" t="s">
+        <v>114</v>
+      </c>
+      <c r="J56" t="s">
+        <v>115</v>
+      </c>
+      <c r="K56" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" t="s">
+        <v>116</v>
+      </c>
+      <c r="M56" t="s">
         <v>117</v>
       </c>
-      <c r="I56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="N56" t="s">
         <v>118</v>
       </c>
-      <c r="K56" t="s">
-        <v>25</v>
-      </c>
-      <c r="L56" t="s">
-        <v>25</v>
-      </c>
-      <c r="M56" t="s">
-        <v>25</v>
-      </c>
-      <c r="N56" t="s">
-        <v>25</v>
-      </c>
       <c r="O56">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P56" s="1">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="R56" t="s">
-        <v>25</v>
-      </c>
-      <c r="S56">
-        <v>3.76</v>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="S56" t="s">
+        <v>26</v>
       </c>
       <c r="T56">
-        <v>1.1000000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="U56">
-        <v>4.21</v>
+        <v>0.79</v>
       </c>
       <c r="V56">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.51</v>
+      </c>
+      <c r="W56">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G57">
         <v>5590</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J57" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L57" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="M57" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="N57" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="O57">
         <v>60</v>
@@ -5054,34 +5090,34 @@
       <c r="P57" s="1">
         <v>0.56699999999999995</v>
       </c>
-      <c r="R57" t="s">
-        <v>25</v>
-      </c>
-      <c r="S57">
+      <c r="S57" t="s">
+        <v>26</v>
+      </c>
+      <c r="T57">
         <v>3.76</v>
       </c>
-      <c r="T57">
+      <c r="U57">
         <v>1.1000000000000001</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <v>4.21</v>
       </c>
-      <c r="V57">
+      <c r="W57">
         <v>0.95</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
         <v>32</v>
@@ -5090,158 +5126,158 @@
         <v>32</v>
       </c>
       <c r="G58">
-        <v>5120</v>
+        <v>5590</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="I58" t="s">
+        <v>114</v>
+      </c>
+      <c r="J58" t="s">
         <v>120</v>
       </c>
-      <c r="J58" t="s">
-        <v>25</v>
-      </c>
       <c r="K58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L58" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="M58" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="N58" t="s">
-        <v>25</v>
-      </c>
-      <c r="O58" t="s">
-        <v>25</v>
+        <v>118</v>
+      </c>
+      <c r="O58">
+        <v>60</v>
       </c>
       <c r="P58" s="1">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="R58">
-        <v>1</v>
-      </c>
-      <c r="S58">
-        <v>4.63</v>
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="S58" t="s">
+        <v>26</v>
       </c>
       <c r="T58">
-        <v>0.62</v>
+        <v>3.76</v>
       </c>
       <c r="U58">
-        <v>4.88</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="V58">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+        <v>4.21</v>
+      </c>
+      <c r="W58">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G59">
         <v>5120</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J59" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="K59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N59" t="s">
-        <v>25</v>
-      </c>
-      <c r="O59">
+        <v>26</v>
+      </c>
+      <c r="O59" t="s">
         <v>26</v>
       </c>
       <c r="P59" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="R59" t="s">
-        <v>25</v>
-      </c>
       <c r="S59">
+        <v>1</v>
+      </c>
+      <c r="T59">
         <v>4.63</v>
       </c>
-      <c r="T59">
+      <c r="U59">
         <v>0.62</v>
       </c>
-      <c r="U59">
+      <c r="V59">
         <v>4.88</v>
       </c>
-      <c r="V59">
+      <c r="W59">
         <v>0.34</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G60">
         <v>5120</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I60" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L60" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="M60" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="O60">
         <v>26</v>
@@ -5249,65 +5285,455 @@
       <c r="P60" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="R60" t="s">
-        <v>25</v>
-      </c>
-      <c r="S60">
+      <c r="S60" t="s">
+        <v>26</v>
+      </c>
+      <c r="T60">
         <v>4.63</v>
       </c>
-      <c r="T60">
+      <c r="U60">
         <v>0.62</v>
       </c>
-      <c r="U60">
+      <c r="V60">
         <v>4.88</v>
       </c>
-      <c r="V60">
+      <c r="W60">
         <v>0.34</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61">
+        <v>5120</v>
+      </c>
+      <c r="H61" t="s">
+        <v>37</v>
+      </c>
+      <c r="I61" t="s">
+        <v>122</v>
+      </c>
+      <c r="J61" t="s">
+        <v>123</v>
+      </c>
+      <c r="K61" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" t="s">
+        <v>124</v>
+      </c>
+      <c r="M61" t="s">
+        <v>125</v>
+      </c>
+      <c r="N61" t="s">
+        <v>126</v>
+      </c>
+      <c r="O61">
+        <v>26</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="S61" t="s">
+        <v>26</v>
+      </c>
+      <c r="T61">
+        <v>4.63</v>
+      </c>
+      <c r="U61">
+        <v>0.62</v>
+      </c>
+      <c r="V61">
+        <v>4.88</v>
+      </c>
+      <c r="W61">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62">
+        <v>5300</v>
+      </c>
+      <c r="H62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" t="s">
+        <v>127</v>
+      </c>
+      <c r="J62" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" t="s">
+        <v>26</v>
+      </c>
+      <c r="O62" t="s">
+        <v>26</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S62">
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <v>4.32</v>
+      </c>
+      <c r="U62">
+        <v>0.9</v>
+      </c>
+      <c r="V62">
+        <v>4.79</v>
+      </c>
+      <c r="W62">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63">
+        <v>5300</v>
+      </c>
+      <c r="H63" t="s">
+        <v>37</v>
+      </c>
+      <c r="I63" t="s">
+        <v>127</v>
+      </c>
+      <c r="J63" t="s">
+        <v>128</v>
+      </c>
+      <c r="K63" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63">
+        <v>50</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S63" t="s">
+        <v>26</v>
+      </c>
+      <c r="T63">
+        <v>4.32</v>
+      </c>
+      <c r="U63">
+        <v>0.9</v>
+      </c>
+      <c r="V63">
+        <v>4.79</v>
+      </c>
+      <c r="W63">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64">
+        <v>5300</v>
+      </c>
+      <c r="H64" t="s">
+        <v>37</v>
+      </c>
+      <c r="I64" t="s">
+        <v>127</v>
+      </c>
+      <c r="J64" t="s">
+        <v>128</v>
+      </c>
+      <c r="K64" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" t="s">
+        <v>129</v>
+      </c>
+      <c r="M64" t="s">
+        <v>130</v>
+      </c>
+      <c r="N64" t="s">
+        <v>131</v>
+      </c>
+      <c r="O64">
+        <v>50</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S64" t="s">
+        <v>26</v>
+      </c>
+      <c r="T64">
+        <v>4.32</v>
+      </c>
+      <c r="U64">
+        <v>0.9</v>
+      </c>
+      <c r="V64">
+        <v>4.8</v>
+      </c>
+      <c r="W64">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65">
+        <v>5300</v>
+      </c>
+      <c r="H65" t="s">
+        <v>37</v>
+      </c>
+      <c r="I65" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>128</v>
+      </c>
+      <c r="K65" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" t="s">
+        <v>129</v>
+      </c>
+      <c r="M65" t="s">
+        <v>132</v>
+      </c>
+      <c r="N65" t="s">
+        <v>133</v>
+      </c>
+      <c r="O65">
+        <v>50</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S65" t="s">
+        <v>26</v>
+      </c>
+      <c r="T65">
+        <v>4.32</v>
+      </c>
+      <c r="U65">
+        <v>0.9</v>
+      </c>
+      <c r="V65">
+        <v>4.88</v>
+      </c>
+      <c r="W65">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66">
+        <v>5300</v>
+      </c>
+      <c r="H66" t="s">
+        <v>37</v>
+      </c>
+      <c r="I66" t="s">
+        <v>127</v>
+      </c>
+      <c r="J66" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="K66" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="M66" t="s">
+        <v>134</v>
+      </c>
+      <c r="N66" t="s">
+        <v>135</v>
+      </c>
+      <c r="O66">
+        <v>50</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S66" t="s">
+        <v>26</v>
+      </c>
+      <c r="T66">
+        <v>4.32</v>
+      </c>
+      <c r="U66">
+        <v>0.9</v>
+      </c>
+      <c r="V66">
+        <v>4.68</v>
+      </c>
+      <c r="W66">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>46082</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46094</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +6011,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F10AEF6-FF50-4564-ABC5-C00E90F498A1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2FEFF6-5E4C-412A-BDA4-BEF1A3C361EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -5593,7 +6019,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EDC754-5AC1-4749-98EC-DCBC89EF2339}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EB9C2B-8465-4B44-AC34-24517D8278E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -5612,7 +6038,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377033B3-E736-4098-B9D1-4FB40012ED70}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32DB3ECF-F876-4867-B1E5-CD57AA4098F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/bm-w26.xlsx
+++ b/bm-w26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{6246EF33-5269-4A79-853D-EE8FFEBC5DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFED0C5F-B0F5-409D-A387-6DF1DA8B8075}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{6246EF33-5269-4A79-853D-EE8FFEBC5DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE51A11-5B3E-4BBB-BC71-B9EB433D6B4B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFF204E3-9B84-4E55-94D5-F8C645A41361}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="143">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
-  </si>
-  <si>
-    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1314,10 +1311,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{595447D4-B5E5-44C0-A029-72E389C850E9}">
-  <dimension ref="A1:W78"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1384,581 +1381,578 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.41099999999999998</v>
       </c>
       <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>19</v>
+      </c>
+      <c r="S2">
+        <v>4.42</v>
+      </c>
+      <c r="T2">
+        <v>0.79</v>
+      </c>
+      <c r="U2">
+        <v>4.59</v>
+      </c>
+      <c r="V2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="S2">
-        <v>19</v>
-      </c>
-      <c r="T2">
-        <v>4.42</v>
-      </c>
-      <c r="U2">
-        <v>0.79</v>
-      </c>
-      <c r="V2">
-        <v>4.59</v>
-      </c>
-      <c r="W2">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="T3">
+        <v>0.73</v>
+      </c>
+      <c r="U3">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="U3">
-        <v>0.73</v>
-      </c>
-      <c r="V3">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="W3">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.43</v>
       </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
       <c r="S4">
-        <v>2</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="T4">
-        <v>4.6900000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="U4">
-        <v>0.5</v>
+        <v>4.74</v>
       </c>
       <c r="V4">
-        <v>4.74</v>
-      </c>
-      <c r="W4">
         <v>0.48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>0.38400000000000001</v>
       </c>
+      <c r="R5">
+        <v>12</v>
+      </c>
       <c r="S5">
-        <v>12</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="T5">
-        <v>4.4400000000000004</v>
+        <v>0.76</v>
       </c>
       <c r="U5">
-        <v>0.76</v>
+        <v>4.55</v>
       </c>
       <c r="V5">
-        <v>4.55</v>
-      </c>
-      <c r="W5">
         <v>0.68</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.56100000000000005</v>
       </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
       <c r="S6">
-        <v>2</v>
+        <v>4.03</v>
       </c>
       <c r="T6">
-        <v>4.03</v>
+        <v>0.98</v>
       </c>
       <c r="U6">
-        <v>0.98</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V6">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="W6">
         <v>0.82</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1">
         <v>0.61499999999999999</v>
       </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
       <c r="S7">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T7">
-        <v>4.63</v>
+        <v>0.62</v>
       </c>
       <c r="U7">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="V7">
-        <v>4.88</v>
-      </c>
-      <c r="W7">
         <v>0.34</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P8" s="1">
         <v>0.5</v>
       </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
       <c r="S8">
-        <v>1</v>
+        <v>4.32</v>
       </c>
       <c r="T8">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U8">
-        <v>0.9</v>
+        <v>4.79</v>
       </c>
       <c r="V8">
-        <v>4.79</v>
-      </c>
-      <c r="W8">
         <v>0.41</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>5100</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1">
         <v>0.17599999999999999</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="T9">
-        <v>4.5599999999999996</v>
+        <v>0.73</v>
       </c>
       <c r="U9">
-        <v>0.73</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="V9">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="W9">
         <v>1.01</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>5100</v>
       </c>
       <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" t="s">
         <v>37</v>
       </c>
-      <c r="I10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" t="s">
-        <v>38</v>
-      </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10">
         <v>51</v>
@@ -1967,66 +1961,66 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="Q10" t="s">
-        <v>29</v>
-      </c>
-      <c r="S10" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>4.5599999999999996</v>
       </c>
       <c r="T10">
-        <v>4.5599999999999996</v>
+        <v>0.73</v>
       </c>
       <c r="U10">
-        <v>0.73</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="V10">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="W10">
         <v>1.01</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11">
         <v>5100</v>
       </c>
       <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" t="s">
         <v>37</v>
       </c>
-      <c r="I11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" t="s">
-        <v>38</v>
-      </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" t="s">
         <v>40</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>41</v>
-      </c>
-      <c r="N11" t="s">
-        <v>42</v>
       </c>
       <c r="O11">
         <v>51</v>
@@ -2035,131 +2029,131 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="Q11" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="T11">
+        <v>0.73</v>
+      </c>
+      <c r="U11">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="V11">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="S11" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="U11">
-        <v>0.73</v>
-      </c>
-      <c r="V11">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="W11">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>5341</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1">
         <v>0.35899999999999999</v>
       </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
       <c r="S12">
-        <v>1</v>
+        <v>4.79</v>
       </c>
       <c r="T12">
-        <v>4.79</v>
+        <v>0.42</v>
       </c>
       <c r="U12">
-        <v>0.42</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="V12">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="W12">
         <v>0.36</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>5341</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" t="s">
         <v>43</v>
       </c>
-      <c r="J13" t="s">
-        <v>44</v>
-      </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O13">
         <v>78</v>
@@ -2167,64 +2161,64 @@
       <c r="P13" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="S13" t="s">
-        <v>26</v>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>4.79</v>
       </c>
       <c r="T13">
-        <v>4.79</v>
+        <v>0.42</v>
       </c>
       <c r="U13">
-        <v>0.42</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="V13">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="W13">
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>5341</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" t="s">
         <v>43</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
         <v>44</v>
       </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>45</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>46</v>
-      </c>
-      <c r="N14" t="s">
-        <v>47</v>
       </c>
       <c r="O14">
         <v>78</v>
@@ -2232,129 +2226,129 @@
       <c r="P14" s="1">
         <v>0.35899999999999999</v>
       </c>
-      <c r="S14" t="s">
-        <v>26</v>
+      <c r="R14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14">
+        <v>4.79</v>
       </c>
       <c r="T14">
-        <v>4.79</v>
+        <v>0.42</v>
       </c>
       <c r="U14">
-        <v>0.42</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="V14">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="W14">
         <v>0.36</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15">
         <v>5347</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1">
         <v>0.5</v>
       </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
       <c r="S15">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T15">
-        <v>4.63</v>
+        <v>0.54</v>
       </c>
       <c r="U15">
-        <v>0.54</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="V15">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="W15">
         <v>0.53</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16">
         <v>5347</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
         <v>48</v>
       </c>
-      <c r="J16" t="s">
-        <v>49</v>
-      </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O16">
         <v>80</v>
@@ -2362,64 +2356,64 @@
       <c r="P16" s="1">
         <v>0.5</v>
       </c>
-      <c r="S16" t="s">
-        <v>26</v>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.63</v>
       </c>
       <c r="T16">
-        <v>4.63</v>
+        <v>0.54</v>
       </c>
       <c r="U16">
-        <v>0.54</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="V16">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="W16">
         <v>0.53</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17">
         <v>5347</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" t="s">
         <v>48</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
         <v>49</v>
       </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>50</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>51</v>
-      </c>
-      <c r="N17" t="s">
-        <v>52</v>
       </c>
       <c r="O17">
         <v>80</v>
@@ -2427,132 +2421,132 @@
       <c r="P17" s="1">
         <v>0.5</v>
       </c>
-      <c r="S17" t="s">
-        <v>26</v>
+      <c r="R17" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17">
+        <v>4.63</v>
       </c>
       <c r="T17">
-        <v>4.63</v>
+        <v>0.54</v>
       </c>
       <c r="U17">
-        <v>0.54</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="V17">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="W17">
         <v>0.53</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18">
         <v>1090</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1">
         <v>0.24399999999999999</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>3.95</v>
       </c>
       <c r="T18">
-        <v>3.95</v>
+        <v>0.97</v>
       </c>
       <c r="U18">
-        <v>0.97</v>
+        <v>4.32</v>
       </c>
       <c r="V18">
-        <v>4.32</v>
-      </c>
-      <c r="W18">
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19">
         <v>1090</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" t="s">
         <v>53</v>
       </c>
-      <c r="J19" t="s">
-        <v>54</v>
-      </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O19">
         <v>78</v>
@@ -2561,66 +2555,66 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
-      </c>
-      <c r="S19" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19">
+        <v>3.95</v>
       </c>
       <c r="T19">
-        <v>3.95</v>
+        <v>0.97</v>
       </c>
       <c r="U19">
-        <v>0.97</v>
+        <v>4.32</v>
       </c>
       <c r="V19">
-        <v>4.32</v>
-      </c>
-      <c r="W19">
         <v>0.75</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20">
         <v>1090</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" t="s">
         <v>53</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
         <v>54</v>
       </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>55</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>56</v>
-      </c>
-      <c r="N20" t="s">
-        <v>57</v>
       </c>
       <c r="O20">
         <v>78</v>
@@ -2629,134 +2623,134 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
-      </c>
-      <c r="S20" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R20" t="s">
+        <v>25</v>
+      </c>
+      <c r="S20">
+        <v>3.95</v>
       </c>
       <c r="T20">
-        <v>3.95</v>
+        <v>0.97</v>
       </c>
       <c r="U20">
-        <v>0.97</v>
+        <v>4.32</v>
       </c>
       <c r="V20">
-        <v>4.32</v>
-      </c>
-      <c r="W20">
         <v>0.75</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <v>1380</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P21" s="1">
         <v>0.27800000000000002</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>4.41</v>
       </c>
       <c r="T21">
-        <v>4.41</v>
+        <v>0.59</v>
       </c>
       <c r="U21">
-        <v>0.59</v>
+        <v>4.55</v>
       </c>
       <c r="V21">
-        <v>4.55</v>
-      </c>
-      <c r="W21">
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <v>1380</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" t="s">
         <v>58</v>
       </c>
-      <c r="J22" t="s">
-        <v>59</v>
-      </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O22">
         <v>79</v>
@@ -2765,66 +2759,66 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
-      </c>
-      <c r="S22" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22">
+        <v>4.41</v>
       </c>
       <c r="T22">
-        <v>4.41</v>
+        <v>0.59</v>
       </c>
       <c r="U22">
-        <v>0.59</v>
+        <v>4.55</v>
       </c>
       <c r="V22">
-        <v>4.55</v>
-      </c>
-      <c r="W22">
         <v>0.6</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>1380</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" t="s">
         <v>58</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
         <v>59</v>
       </c>
-      <c r="K23" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>60</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>61</v>
-      </c>
-      <c r="N23" t="s">
-        <v>62</v>
       </c>
       <c r="O23">
         <v>79</v>
@@ -2833,131 +2827,131 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
-      </c>
-      <c r="S23" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R23" t="s">
+        <v>25</v>
+      </c>
+      <c r="S23">
+        <v>4.41</v>
       </c>
       <c r="T23">
-        <v>4.41</v>
+        <v>0.59</v>
       </c>
       <c r="U23">
-        <v>0.59</v>
+        <v>4.55</v>
       </c>
       <c r="V23">
-        <v>4.55</v>
-      </c>
-      <c r="W23">
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>1700</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P24" s="1">
         <v>0.34799999999999998</v>
       </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
       <c r="S24">
-        <v>1</v>
+        <v>4.43</v>
       </c>
       <c r="T24">
-        <v>4.43</v>
+        <v>0.7</v>
       </c>
       <c r="U24">
-        <v>0.7</v>
+        <v>4.57</v>
       </c>
       <c r="V24">
-        <v>4.57</v>
-      </c>
-      <c r="W24">
         <v>0.63</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>1700</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" t="s">
         <v>63</v>
       </c>
-      <c r="J25" t="s">
-        <v>64</v>
-      </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O25">
         <v>198</v>
@@ -2965,64 +2959,64 @@
       <c r="P25" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="S25" t="s">
-        <v>26</v>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25">
+        <v>4.43</v>
       </c>
       <c r="T25">
-        <v>4.43</v>
+        <v>0.7</v>
       </c>
       <c r="U25">
-        <v>0.7</v>
+        <v>4.57</v>
       </c>
       <c r="V25">
-        <v>4.57</v>
-      </c>
-      <c r="W25">
         <v>0.63</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>1700</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" t="s">
         <v>63</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" t="s">
         <v>64</v>
       </c>
-      <c r="K26" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>65</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>66</v>
-      </c>
-      <c r="N26" t="s">
-        <v>67</v>
       </c>
       <c r="O26">
         <v>198</v>
@@ -3030,132 +3024,132 @@
       <c r="P26" s="1">
         <v>0.34799999999999998</v>
       </c>
-      <c r="S26" t="s">
-        <v>26</v>
+      <c r="R26" t="s">
+        <v>25</v>
+      </c>
+      <c r="S26">
+        <v>4.43</v>
       </c>
       <c r="T26">
-        <v>4.43</v>
+        <v>0.7</v>
       </c>
       <c r="U26">
-        <v>0.7</v>
+        <v>4.57</v>
       </c>
       <c r="V26">
-        <v>4.57</v>
-      </c>
-      <c r="W26">
         <v>0.63</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27">
         <v>2400</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P27" s="1">
         <v>0.28000000000000003</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>4.07</v>
       </c>
       <c r="T27">
-        <v>4.07</v>
+        <v>0.9</v>
       </c>
       <c r="U27">
-        <v>0.9</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V27">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="W27">
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28">
         <v>2400</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" t="s">
         <v>68</v>
       </c>
-      <c r="J28" t="s">
-        <v>69</v>
-      </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -3164,66 +3158,66 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q28" t="s">
-        <v>29</v>
-      </c>
-      <c r="S28" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R28" t="s">
+        <v>25</v>
+      </c>
+      <c r="S28">
+        <v>4.07</v>
       </c>
       <c r="T28">
-        <v>4.07</v>
+        <v>0.9</v>
       </c>
       <c r="U28">
-        <v>0.9</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V28">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="W28">
         <v>0.83</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29">
         <v>2400</v>
       </c>
       <c r="H29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" t="s">
         <v>68</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" t="s">
         <v>69</v>
       </c>
-      <c r="K29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>70</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>71</v>
-      </c>
-      <c r="N29" t="s">
-        <v>72</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -3232,134 +3226,134 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
-      </c>
-      <c r="S29" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R29" t="s">
+        <v>25</v>
+      </c>
+      <c r="S29">
+        <v>4.07</v>
       </c>
       <c r="T29">
-        <v>4.07</v>
+        <v>0.9</v>
       </c>
       <c r="U29">
-        <v>0.9</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V29">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="W29">
         <v>0.83</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30">
         <v>4010</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P30" s="1">
         <v>0.435</v>
       </c>
       <c r="Q30" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
       </c>
       <c r="S30">
-        <v>1</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="T30">
+        <v>0.32</v>
+      </c>
+      <c r="U30">
         <v>4.9000000000000004</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>0.32</v>
       </c>
-      <c r="V30">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="W30">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31">
         <v>4010</v>
       </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31" t="s">
         <v>73</v>
       </c>
-      <c r="J31" t="s">
-        <v>74</v>
-      </c>
       <c r="K31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O31">
         <v>23</v>
@@ -3368,66 +3362,66 @@
         <v>0.435</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R31" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31">
+        <v>4.9000000000000004</v>
       </c>
       <c r="T31">
+        <v>0.32</v>
+      </c>
+      <c r="U31">
         <v>4.9000000000000004</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>0.32</v>
       </c>
-      <c r="V31">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="W31">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32">
         <v>4010</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" t="s">
         <v>73</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" t="s">
         <v>74</v>
       </c>
-      <c r="K32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>75</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>76</v>
-      </c>
-      <c r="N32" t="s">
-        <v>77</v>
       </c>
       <c r="O32">
         <v>23</v>
@@ -3436,134 +3430,134 @@
         <v>0.435</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S32" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R32" t="s">
+        <v>25</v>
+      </c>
+      <c r="S32">
+        <v>4.9000000000000004</v>
       </c>
       <c r="T32">
+        <v>0.32</v>
+      </c>
+      <c r="U32">
         <v>4.9000000000000004</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>0.32</v>
       </c>
-      <c r="V32">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="W32">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G33">
         <v>4740</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P33" s="1">
         <v>0.36399999999999999</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
       </c>
       <c r="S33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V33">
-        <v>4.5</v>
-      </c>
-      <c r="W33">
         <v>0.76</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34">
         <v>4740</v>
       </c>
       <c r="H34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s">
         <v>78</v>
       </c>
-      <c r="J34" t="s">
-        <v>79</v>
-      </c>
       <c r="K34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O34">
         <v>22</v>
@@ -3572,66 +3566,66 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="Q34" t="s">
-        <v>29</v>
-      </c>
-      <c r="S34" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R34" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34">
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V34">
-        <v>4.5</v>
-      </c>
-      <c r="W34">
         <v>0.76</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G35">
         <v>4740</v>
       </c>
       <c r="H35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s">
         <v>78</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
         <v>79</v>
       </c>
-      <c r="K35" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>80</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>81</v>
-      </c>
-      <c r="N35" t="s">
-        <v>82</v>
       </c>
       <c r="O35">
         <v>22</v>
@@ -3640,131 +3634,131 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="Q35" t="s">
-        <v>29</v>
-      </c>
-      <c r="S35" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R35" t="s">
+        <v>25</v>
+      </c>
+      <c r="S35">
+        <v>5</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V35">
-        <v>4.5</v>
-      </c>
-      <c r="W35">
         <v>0.76</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G36">
         <v>5220</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P36" s="1">
         <v>0.64600000000000002</v>
       </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
       <c r="S36">
-        <v>1</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="T36">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="U36">
-        <v>0.56000000000000005</v>
+        <v>4.58</v>
       </c>
       <c r="V36">
-        <v>4.58</v>
-      </c>
-      <c r="W36">
         <v>0.62</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37">
         <v>5220</v>
       </c>
       <c r="H37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s">
+        <v>82</v>
+      </c>
+      <c r="J37" t="s">
         <v>83</v>
       </c>
-      <c r="J37" t="s">
-        <v>84</v>
-      </c>
       <c r="K37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O37">
         <v>48</v>
@@ -3772,64 +3766,64 @@
       <c r="P37" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="S37" t="s">
-        <v>26</v>
+      <c r="R37" t="s">
+        <v>25</v>
+      </c>
+      <c r="S37">
+        <v>4.6100000000000003</v>
       </c>
       <c r="T37">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="U37">
-        <v>0.56000000000000005</v>
+        <v>4.58</v>
       </c>
       <c r="V37">
-        <v>4.58</v>
-      </c>
-      <c r="W37">
         <v>0.62</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38">
         <v>5220</v>
       </c>
       <c r="H38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s">
         <v>83</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" t="s">
         <v>84</v>
       </c>
-      <c r="K38" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>85</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>86</v>
-      </c>
-      <c r="N38" t="s">
-        <v>87</v>
       </c>
       <c r="O38">
         <v>48</v>
@@ -3837,129 +3831,129 @@
       <c r="P38" s="1">
         <v>0.64600000000000002</v>
       </c>
-      <c r="S38" t="s">
-        <v>26</v>
+      <c r="R38" t="s">
+        <v>25</v>
+      </c>
+      <c r="S38">
+        <v>4.6100000000000003</v>
       </c>
       <c r="T38">
-        <v>4.6100000000000003</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="U38">
-        <v>0.56000000000000005</v>
+        <v>4.58</v>
       </c>
       <c r="V38">
-        <v>4.58</v>
-      </c>
-      <c r="W38">
         <v>0.62</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39">
         <v>5720</v>
       </c>
       <c r="H39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P39" s="1">
         <v>0.61099999999999999</v>
       </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
       <c r="S39">
-        <v>1</v>
+        <v>4.45</v>
       </c>
       <c r="T39">
-        <v>4.45</v>
+        <v>0.83</v>
       </c>
       <c r="U39">
+        <v>4.55</v>
+      </c>
+      <c r="V39">
         <v>0.83</v>
       </c>
-      <c r="V39">
-        <v>4.55</v>
-      </c>
-      <c r="W39">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40">
         <v>5720</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" t="s">
         <v>88</v>
       </c>
-      <c r="J40" t="s">
-        <v>89</v>
-      </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O40">
         <v>54</v>
@@ -3967,64 +3961,64 @@
       <c r="P40" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="S40" t="s">
-        <v>26</v>
+      <c r="R40" t="s">
+        <v>25</v>
+      </c>
+      <c r="S40">
+        <v>4.45</v>
       </c>
       <c r="T40">
-        <v>4.45</v>
+        <v>0.83</v>
       </c>
       <c r="U40">
+        <v>4.55</v>
+      </c>
+      <c r="V40">
         <v>0.83</v>
       </c>
-      <c r="V40">
-        <v>4.55</v>
-      </c>
-      <c r="W40">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G41">
         <v>5720</v>
       </c>
       <c r="H41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I41" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" t="s">
         <v>88</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" t="s">
         <v>89</v>
       </c>
-      <c r="K41" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" t="s">
-        <v>90</v>
-      </c>
       <c r="M41" t="s">
+        <v>65</v>
+      </c>
+      <c r="N41" t="s">
         <v>66</v>
-      </c>
-      <c r="N41" t="s">
-        <v>67</v>
       </c>
       <c r="O41">
         <v>54</v>
@@ -4032,129 +4026,129 @@
       <c r="P41" s="1">
         <v>0.61099999999999999</v>
       </c>
-      <c r="S41" t="s">
-        <v>26</v>
+      <c r="R41" t="s">
+        <v>25</v>
+      </c>
+      <c r="S41">
+        <v>4.45</v>
       </c>
       <c r="T41">
-        <v>4.45</v>
+        <v>0.83</v>
       </c>
       <c r="U41">
+        <v>4.55</v>
+      </c>
+      <c r="V41">
         <v>0.83</v>
       </c>
-      <c r="V41">
-        <v>4.55</v>
-      </c>
-      <c r="W41">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G42">
         <v>5745</v>
       </c>
       <c r="H42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P42" s="1">
         <v>0.45</v>
       </c>
+      <c r="R42">
+        <v>1</v>
+      </c>
       <c r="S42">
-        <v>1</v>
+        <v>4.78</v>
       </c>
       <c r="T42">
-        <v>4.78</v>
+        <v>0.42</v>
       </c>
       <c r="U42">
-        <v>0.42</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="V42">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="W42">
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43">
         <v>5745</v>
       </c>
       <c r="H43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s">
+        <v>90</v>
+      </c>
+      <c r="J43" t="s">
         <v>91</v>
       </c>
-      <c r="J43" t="s">
-        <v>92</v>
-      </c>
       <c r="K43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O43">
         <v>60</v>
@@ -4162,64 +4156,64 @@
       <c r="P43" s="1">
         <v>0.45</v>
       </c>
-      <c r="S43" t="s">
-        <v>26</v>
+      <c r="R43" t="s">
+        <v>25</v>
+      </c>
+      <c r="S43">
+        <v>4.78</v>
       </c>
       <c r="T43">
-        <v>4.78</v>
+        <v>0.42</v>
       </c>
       <c r="U43">
-        <v>0.42</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="V43">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="W43">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44">
         <v>5745</v>
       </c>
       <c r="H44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
+        <v>90</v>
+      </c>
+      <c r="J44" t="s">
         <v>91</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" t="s">
         <v>92</v>
       </c>
-      <c r="K44" t="s">
-        <v>26</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>93</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>94</v>
-      </c>
-      <c r="N44" t="s">
-        <v>95</v>
       </c>
       <c r="O44">
         <v>60</v>
@@ -4227,129 +4221,129 @@
       <c r="P44" s="1">
         <v>0.45</v>
       </c>
-      <c r="S44" t="s">
-        <v>26</v>
+      <c r="R44" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44">
+        <v>4.78</v>
       </c>
       <c r="T44">
-        <v>4.78</v>
+        <v>0.42</v>
       </c>
       <c r="U44">
-        <v>0.42</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="V44">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="W44">
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
         <v>96</v>
       </c>
-      <c r="H45" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45" t="s">
-        <v>97</v>
-      </c>
       <c r="J45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P45" s="1">
         <v>0.77800000000000002</v>
       </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
       <c r="S45">
-        <v>1</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="T45">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
       </c>
       <c r="U45">
-        <v>0.77</v>
+        <v>4.43</v>
       </c>
       <c r="V45">
-        <v>4.43</v>
-      </c>
-      <c r="W45">
         <v>0.65</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
         <v>96</v>
       </c>
-      <c r="H46" t="s">
-        <v>37</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>97</v>
       </c>
-      <c r="J46" t="s">
-        <v>98</v>
-      </c>
       <c r="K46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O46">
         <v>18</v>
@@ -4357,64 +4351,64 @@
       <c r="P46" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="S46" t="s">
-        <v>26</v>
+      <c r="R46" t="s">
+        <v>25</v>
+      </c>
+      <c r="S46">
+        <v>4.1399999999999997</v>
       </c>
       <c r="T46">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
       </c>
       <c r="U46">
-        <v>0.77</v>
+        <v>4.43</v>
       </c>
       <c r="V46">
-        <v>4.43</v>
-      </c>
-      <c r="W46">
         <v>0.65</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" t="s">
         <v>96</v>
       </c>
-      <c r="H47" t="s">
-        <v>37</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>97</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" t="s">
         <v>98</v>
       </c>
-      <c r="K47" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" t="s">
+      <c r="M47" t="s">
         <v>99</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>100</v>
-      </c>
-      <c r="N47" t="s">
-        <v>101</v>
       </c>
       <c r="O47">
         <v>18</v>
@@ -4422,132 +4416,132 @@
       <c r="P47" s="1">
         <v>0.77800000000000002</v>
       </c>
-      <c r="S47" t="s">
-        <v>26</v>
+      <c r="R47" t="s">
+        <v>25</v>
+      </c>
+      <c r="S47">
+        <v>4.1399999999999997</v>
       </c>
       <c r="T47">
-        <v>4.1399999999999997</v>
+        <v>0.77</v>
       </c>
       <c r="U47">
-        <v>0.77</v>
+        <v>4.43</v>
       </c>
       <c r="V47">
-        <v>4.43</v>
-      </c>
-      <c r="W47">
         <v>0.65</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
+        <v>101</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" t="s">
         <v>102</v>
       </c>
-      <c r="H48" t="s">
-        <v>26</v>
-      </c>
-      <c r="I48" t="s">
-        <v>103</v>
-      </c>
       <c r="J48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P48" s="1">
         <v>0.53600000000000003</v>
       </c>
       <c r="Q48" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
       </c>
       <c r="S48">
-        <v>1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="T48">
-        <v>4.4000000000000004</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U48">
-        <v>1.1200000000000001</v>
+        <v>4.53</v>
       </c>
       <c r="V48">
-        <v>4.53</v>
-      </c>
-      <c r="W48">
         <v>0.83</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
+        <v>101</v>
+      </c>
+      <c r="H49" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" t="s">
         <v>102</v>
       </c>
-      <c r="H49" t="s">
-        <v>37</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>103</v>
       </c>
-      <c r="J49" t="s">
-        <v>104</v>
-      </c>
       <c r="K49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O49">
         <v>28</v>
@@ -4556,66 +4550,66 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="Q49" t="s">
-        <v>29</v>
-      </c>
-      <c r="S49" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R49" t="s">
+        <v>25</v>
+      </c>
+      <c r="S49">
+        <v>4.4000000000000004</v>
       </c>
       <c r="T49">
-        <v>4.4000000000000004</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U49">
-        <v>1.1200000000000001</v>
+        <v>4.53</v>
       </c>
       <c r="V49">
-        <v>4.53</v>
-      </c>
-      <c r="W49">
         <v>0.83</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
+        <v>101</v>
+      </c>
+      <c r="H50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" t="s">
         <v>102</v>
       </c>
-      <c r="H50" t="s">
-        <v>37</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>103</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" t="s">
         <v>104</v>
       </c>
-      <c r="K50" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" t="s">
+      <c r="M50" t="s">
         <v>105</v>
       </c>
-      <c r="M50" t="s">
+      <c r="N50" t="s">
         <v>106</v>
-      </c>
-      <c r="N50" t="s">
-        <v>107</v>
       </c>
       <c r="O50">
         <v>28</v>
@@ -4624,134 +4618,134 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="Q50" t="s">
-        <v>29</v>
-      </c>
-      <c r="S50" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R50" t="s">
+        <v>25</v>
+      </c>
+      <c r="S50">
+        <v>4.4000000000000004</v>
       </c>
       <c r="T50">
-        <v>4.4000000000000004</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U50">
-        <v>1.1200000000000001</v>
+        <v>4.53</v>
       </c>
       <c r="V50">
-        <v>4.53</v>
-      </c>
-      <c r="W50">
         <v>0.83</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
+        <v>107</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" t="s">
         <v>108</v>
       </c>
-      <c r="H51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" t="s">
-        <v>109</v>
-      </c>
       <c r="J51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P51" s="1">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q51" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
         <v>5</v>
       </c>
-      <c r="U51">
+      <c r="V51">
         <v>0</v>
       </c>
-      <c r="V51">
-        <v>5</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
+        <v>107</v>
+      </c>
+      <c r="H52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" t="s">
         <v>108</v>
       </c>
-      <c r="H52" t="s">
-        <v>37</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>109</v>
       </c>
-      <c r="J52" t="s">
-        <v>110</v>
-      </c>
       <c r="K52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O52">
         <v>13</v>
@@ -4760,66 +4754,66 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q52" t="s">
-        <v>29</v>
-      </c>
-      <c r="S52" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R52" t="s">
+        <v>25</v>
+      </c>
+      <c r="S52">
+        <v>5</v>
       </c>
       <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
         <v>5</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <v>0</v>
       </c>
-      <c r="V52">
-        <v>5</v>
-      </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" t="s">
+        <v>107</v>
+      </c>
+      <c r="H53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" t="s">
         <v>108</v>
       </c>
-      <c r="H53" t="s">
-        <v>37</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>109</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
         <v>110</v>
       </c>
-      <c r="K53" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>111</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>112</v>
-      </c>
-      <c r="N53" t="s">
-        <v>113</v>
       </c>
       <c r="O53">
         <v>13</v>
@@ -4828,131 +4822,131 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q53" t="s">
-        <v>29</v>
-      </c>
-      <c r="S53" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R53" t="s">
+        <v>25</v>
+      </c>
+      <c r="S53">
+        <v>5</v>
       </c>
       <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
         <v>5</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>0</v>
       </c>
-      <c r="V53">
-        <v>5</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G54">
         <v>5590</v>
       </c>
       <c r="H54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P54" s="1">
         <v>0.56100000000000005</v>
       </c>
+      <c r="R54">
+        <v>2</v>
+      </c>
       <c r="S54">
-        <v>2</v>
+        <v>4.03</v>
       </c>
       <c r="T54">
-        <v>4.03</v>
+        <v>0.98</v>
       </c>
       <c r="U54">
-        <v>0.98</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="V54">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="W54">
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G55">
         <v>5590</v>
       </c>
       <c r="H55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
+        <v>113</v>
+      </c>
+      <c r="J55" t="s">
         <v>114</v>
       </c>
-      <c r="J55" t="s">
-        <v>115</v>
-      </c>
       <c r="K55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O55">
         <v>63</v>
@@ -4960,64 +4954,64 @@
       <c r="P55" s="1">
         <v>0.55600000000000005</v>
       </c>
-      <c r="S55" t="s">
-        <v>26</v>
+      <c r="R55" t="s">
+        <v>25</v>
+      </c>
+      <c r="S55">
+        <v>4.29</v>
       </c>
       <c r="T55">
-        <v>4.29</v>
+        <v>0.79</v>
       </c>
       <c r="U55">
-        <v>0.79</v>
+        <v>4.51</v>
       </c>
       <c r="V55">
-        <v>4.51</v>
-      </c>
-      <c r="W55">
         <v>0.66</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G56">
         <v>5590</v>
       </c>
       <c r="H56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s">
+        <v>113</v>
+      </c>
+      <c r="J56" t="s">
         <v>114</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" t="s">
         <v>115</v>
       </c>
-      <c r="K56" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>116</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>117</v>
-      </c>
-      <c r="N56" t="s">
-        <v>118</v>
       </c>
       <c r="O56">
         <v>63</v>
@@ -5025,64 +5019,64 @@
       <c r="P56" s="1">
         <v>0.55600000000000005</v>
       </c>
-      <c r="S56" t="s">
-        <v>26</v>
+      <c r="R56" t="s">
+        <v>25</v>
+      </c>
+      <c r="S56">
+        <v>4.29</v>
       </c>
       <c r="T56">
-        <v>4.29</v>
+        <v>0.79</v>
       </c>
       <c r="U56">
-        <v>0.79</v>
+        <v>4.51</v>
       </c>
       <c r="V56">
-        <v>4.51</v>
-      </c>
-      <c r="W56">
         <v>0.66</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G57">
         <v>5590</v>
       </c>
       <c r="H57" t="s">
+        <v>118</v>
+      </c>
+      <c r="I57" t="s">
+        <v>113</v>
+      </c>
+      <c r="J57" t="s">
         <v>119</v>
       </c>
-      <c r="I57" t="s">
-        <v>114</v>
-      </c>
-      <c r="J57" t="s">
-        <v>120</v>
-      </c>
       <c r="K57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O57">
         <v>60</v>
@@ -5090,64 +5084,64 @@
       <c r="P57" s="1">
         <v>0.56699999999999995</v>
       </c>
-      <c r="S57" t="s">
-        <v>26</v>
+      <c r="R57" t="s">
+        <v>25</v>
+      </c>
+      <c r="S57">
+        <v>3.76</v>
       </c>
       <c r="T57">
-        <v>3.76</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="U57">
-        <v>1.1000000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="V57">
-        <v>4.21</v>
-      </c>
-      <c r="W57">
         <v>0.95</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G58">
         <v>5590</v>
       </c>
       <c r="H58" t="s">
+        <v>118</v>
+      </c>
+      <c r="I58" t="s">
+        <v>113</v>
+      </c>
+      <c r="J58" t="s">
         <v>119</v>
       </c>
-      <c r="I58" t="s">
-        <v>114</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" t="s">
         <v>120</v>
       </c>
-      <c r="K58" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" t="s">
-        <v>121</v>
-      </c>
       <c r="M58" t="s">
+        <v>116</v>
+      </c>
+      <c r="N58" t="s">
         <v>117</v>
-      </c>
-      <c r="N58" t="s">
-        <v>118</v>
       </c>
       <c r="O58">
         <v>60</v>
@@ -5155,129 +5149,129 @@
       <c r="P58" s="1">
         <v>0.56699999999999995</v>
       </c>
-      <c r="S58" t="s">
-        <v>26</v>
+      <c r="R58" t="s">
+        <v>25</v>
+      </c>
+      <c r="S58">
+        <v>3.76</v>
       </c>
       <c r="T58">
-        <v>3.76</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="U58">
-        <v>1.1000000000000001</v>
+        <v>4.21</v>
       </c>
       <c r="V58">
-        <v>4.21</v>
-      </c>
-      <c r="W58">
         <v>0.95</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G59">
         <v>5120</v>
       </c>
       <c r="H59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P59" s="1">
         <v>0.61499999999999999</v>
       </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
       <c r="S59">
-        <v>1</v>
+        <v>4.63</v>
       </c>
       <c r="T59">
-        <v>4.63</v>
+        <v>0.62</v>
       </c>
       <c r="U59">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="V59">
-        <v>4.88</v>
-      </c>
-      <c r="W59">
         <v>0.34</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>7</v>
       </c>
       <c r="D60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G60">
         <v>5120</v>
       </c>
       <c r="H60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I60" t="s">
+        <v>121</v>
+      </c>
+      <c r="J60" t="s">
         <v>122</v>
       </c>
-      <c r="J60" t="s">
-        <v>123</v>
-      </c>
       <c r="K60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O60">
         <v>26</v>
@@ -5285,64 +5279,64 @@
       <c r="P60" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="S60" t="s">
-        <v>26</v>
+      <c r="R60" t="s">
+        <v>25</v>
+      </c>
+      <c r="S60">
+        <v>4.63</v>
       </c>
       <c r="T60">
-        <v>4.63</v>
+        <v>0.62</v>
       </c>
       <c r="U60">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="V60">
-        <v>4.88</v>
-      </c>
-      <c r="W60">
         <v>0.34</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G61">
         <v>5120</v>
       </c>
       <c r="H61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s">
+        <v>121</v>
+      </c>
+      <c r="J61" t="s">
         <v>122</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" t="s">
         <v>123</v>
       </c>
-      <c r="K61" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>124</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>125</v>
-      </c>
-      <c r="N61" t="s">
-        <v>126</v>
       </c>
       <c r="O61">
         <v>26</v>
@@ -5350,129 +5344,129 @@
       <c r="P61" s="1">
         <v>0.61499999999999999</v>
       </c>
-      <c r="S61" t="s">
-        <v>26</v>
+      <c r="R61" t="s">
+        <v>25</v>
+      </c>
+      <c r="S61">
+        <v>4.63</v>
       </c>
       <c r="T61">
-        <v>4.63</v>
+        <v>0.62</v>
       </c>
       <c r="U61">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="V61">
-        <v>4.88</v>
-      </c>
-      <c r="W61">
         <v>0.34</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G62">
         <v>5300</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P62" s="1">
         <v>0.5</v>
       </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
       <c r="S62">
-        <v>1</v>
+        <v>4.32</v>
       </c>
       <c r="T62">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U62">
-        <v>0.9</v>
+        <v>4.79</v>
       </c>
       <c r="V62">
-        <v>4.79</v>
-      </c>
-      <c r="W62">
         <v>0.41</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G63">
         <v>5300</v>
       </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s">
+        <v>126</v>
+      </c>
+      <c r="J63" t="s">
         <v>127</v>
       </c>
-      <c r="J63" t="s">
-        <v>128</v>
-      </c>
       <c r="K63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O63">
         <v>50</v>
@@ -5480,64 +5474,64 @@
       <c r="P63" s="1">
         <v>0.5</v>
       </c>
-      <c r="S63" t="s">
-        <v>26</v>
+      <c r="R63" t="s">
+        <v>25</v>
+      </c>
+      <c r="S63">
+        <v>4.32</v>
       </c>
       <c r="T63">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U63">
-        <v>0.9</v>
+        <v>4.79</v>
       </c>
       <c r="V63">
-        <v>4.79</v>
-      </c>
-      <c r="W63">
         <v>0.41</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G64">
         <v>5300</v>
       </c>
       <c r="H64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
+        <v>126</v>
+      </c>
+      <c r="J64" t="s">
         <v>127</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" t="s">
         <v>128</v>
       </c>
-      <c r="K64" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" t="s">
+      <c r="M64" t="s">
         <v>129</v>
       </c>
-      <c r="M64" t="s">
+      <c r="N64" t="s">
         <v>130</v>
-      </c>
-      <c r="N64" t="s">
-        <v>131</v>
       </c>
       <c r="O64">
         <v>50</v>
@@ -5545,64 +5539,64 @@
       <c r="P64" s="1">
         <v>0.5</v>
       </c>
-      <c r="S64" t="s">
-        <v>26</v>
+      <c r="R64" t="s">
+        <v>25</v>
+      </c>
+      <c r="S64">
+        <v>4.32</v>
       </c>
       <c r="T64">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U64">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="V64">
-        <v>4.8</v>
-      </c>
-      <c r="W64">
         <v>0.41</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G65">
         <v>5300</v>
       </c>
       <c r="H65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I65" t="s">
+        <v>126</v>
+      </c>
+      <c r="J65" t="s">
         <v>127</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" t="s">
         <v>128</v>
       </c>
-      <c r="K65" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" t="s">
-        <v>129</v>
-      </c>
       <c r="M65" t="s">
+        <v>131</v>
+      </c>
+      <c r="N65" t="s">
         <v>132</v>
-      </c>
-      <c r="N65" t="s">
-        <v>133</v>
       </c>
       <c r="O65">
         <v>50</v>
@@ -5610,64 +5604,64 @@
       <c r="P65" s="1">
         <v>0.5</v>
       </c>
-      <c r="S65" t="s">
-        <v>26</v>
+      <c r="R65" t="s">
+        <v>25</v>
+      </c>
+      <c r="S65">
+        <v>4.32</v>
       </c>
       <c r="T65">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U65">
-        <v>0.9</v>
+        <v>4.88</v>
       </c>
       <c r="V65">
-        <v>4.88</v>
-      </c>
-      <c r="W65">
         <v>0.33</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G66">
         <v>5300</v>
       </c>
       <c r="H66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I66" t="s">
+        <v>126</v>
+      </c>
+      <c r="J66" t="s">
         <v>127</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" t="s">
         <v>128</v>
       </c>
-      <c r="K66" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" t="s">
-        <v>129</v>
-      </c>
       <c r="M66" t="s">
+        <v>133</v>
+      </c>
+      <c r="N66" t="s">
         <v>134</v>
-      </c>
-      <c r="N66" t="s">
-        <v>135</v>
       </c>
       <c r="O66">
         <v>50</v>
@@ -5675,63 +5669,63 @@
       <c r="P66" s="1">
         <v>0.5</v>
       </c>
-      <c r="S66" t="s">
-        <v>26</v>
+      <c r="R66" t="s">
+        <v>25</v>
+      </c>
+      <c r="S66">
+        <v>4.32</v>
       </c>
       <c r="T66">
-        <v>4.32</v>
+        <v>0.9</v>
       </c>
       <c r="U66">
-        <v>0.9</v>
+        <v>4.68</v>
       </c>
       <c r="V66">
-        <v>4.68</v>
-      </c>
-      <c r="W66">
         <v>0.48</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>46094</v>
       </c>
@@ -5742,15 +5736,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -5999,6 +5984,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6011,14 +6005,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2FEFF6-5E4C-412A-BDA4-BEF1A3C361EA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EB9C2B-8465-4B44-AC34-24517D8278E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6037,6 +6023,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2FEFF6-5E4C-412A-BDA4-BEF1A3C361EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32DB3ECF-F876-4867-B1E5-CD57AA4098F0}">
   <ds:schemaRefs>
